--- a/退職金_確定拠出年金_重複調整シミュレーション.xlsx
+++ b/退職金_確定拠出年金_重複調整シミュレーション.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\personal\克彦\40_個人年金\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D80A33D1-0043-48BC-BDB2-4111BAFFDE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2775A7F1-AD0F-4FFD-B397-E20A4ADFED41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1175,7 +1175,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1204,19 +1204,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <protection hidden="1"/>
@@ -1252,31 +1239,12 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1285,18 +1253,6 @@
     </xf>
     <xf numFmtId="177" fontId="0" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1430,16 +1386,56 @@
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1489,7 +1485,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$R$12:$T$20" spid="_x0000_s4330"/>
+                  <a14:cameraTool cellRange="$R$12:$T$20" spid="_x0000_s4333"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1554,7 +1550,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$N$12:$O$18" spid="_x0000_s4331"/>
+                  <a14:cameraTool cellRange="$N$12:$O$18" spid="_x0000_s4334"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1619,7 +1615,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$V$12:$V$15" spid="_x0000_s4332"/>
+                  <a14:cameraTool cellRange="$V$12:$V$15" spid="_x0000_s4335"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1979,54 +1975,54 @@
   <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="34" style="16" customWidth="1"/>
-    <col min="2" max="2" width="22.25" style="16" customWidth="1"/>
-    <col min="3" max="3" width="96.875" style="16" customWidth="1"/>
-    <col min="4" max="4" width="8.5" style="16" customWidth="1"/>
-    <col min="5" max="5" width="9" style="17"/>
-    <col min="6" max="6" width="11.375" style="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="17"/>
+    <col min="1" max="1" width="34" style="10" customWidth="1"/>
+    <col min="2" max="2" width="22.25" style="10" customWidth="1"/>
+    <col min="3" max="3" width="96.875" style="10" customWidth="1"/>
+    <col min="4" max="4" width="8.5" style="10" customWidth="1"/>
+    <col min="5" max="5" width="9" style="11"/>
+    <col min="6" max="6" width="11.375" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="63" t="s">
         <v>230</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="10" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="10" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="13" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="7">
         <v>32599</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="11" t="s">
         <v>210</v>
       </c>
       <c r="F6" s="6">
@@ -2034,331 +2030,331 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="13" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="7">
         <v>49459</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="F7" s="21" t="str">
+      <c r="F7" s="15" t="str">
         <f>DATEDIF($F$6, B7, "Y") &amp; "歳" &amp; DATEDIF($F$6, B7, "YM") &amp; "ヶ月"</f>
         <v>65歳0ヶ月</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="13" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="7">
         <v>49459</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="13" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="8">
         <v>1000000</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="13" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="7">
         <v>44652</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="13" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="13" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="7">
         <v>49825</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="F11" s="17" t="str">
+      <c r="F11" s="11" t="str">
         <f>DATEDIF($F$6, B11, "Y") &amp; "歳" &amp; DATEDIF($F$6, B11, "YM") &amp; "ヶ月"</f>
         <v>66歳0ヶ月</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="13" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="7">
         <v>46172</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="13" t="s">
         <v>16</v>
       </c>
       <c r="B13" s="8">
         <v>10000000</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="16">
         <v>19</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="13" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="22">
+      <c r="B15" s="16">
         <v>9</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="13" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="10" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="16" t="str">
+      <c r="B17" s="10" t="str">
         <f>IF(OR(B8="",B12=""),"",IF(B12&lt;B8,"DC → 会社退職金",IF(B12&gt;B8,"会社退職金 → DC","同日受取：要確認")))</f>
         <v>DC → 会社退職金</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="12" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B19" s="17">
         <f>IF(OR(B6="",B7=""),"",DATEDIF(B6,B7+1,"Y")+IF(DATEDIF(B6,B7+1,"YM")+DATEDIF(B6,B7+1,"MD")&gt;0,1,0))</f>
         <v>47</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="13" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="23">
+      <c r="B20" s="17">
         <f>IF(B19="","",IF(B19&lt;=20,MAX(800000,400000*B19),8000000+700000*(B19-20)))</f>
         <v>26900000</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="13" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B21" s="17">
         <f>IF(OR(B10="",B11=""),"",DATEDIF(B10,B11+1,"Y")+IF(DATEDIF(B10,B11+1,"YM")+DATEDIF(B10,B11+1,"MD")&gt;0,1,0))</f>
         <v>15</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="13" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="23">
+      <c r="B22" s="17">
         <f>IF(B21="","",IF(B21&lt;=20,MAX(800000,400000*B21),8000000+700000*(B21-20)))</f>
         <v>6000000</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="13" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="10">
         <f>IF(B17="DC → 会社退職金",9,IF(B17="会社退職金 → DC",19,""))</f>
         <v>9</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="10" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="10" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="24"/>
+      <c r="C25" s="62"/>
     </row>
     <row r="27" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="18" t="s">
+      <c r="A27" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="24" t="s">
+      <c r="B27" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="24"/>
-      <c r="D27" s="19"/>
+      <c r="C27" s="62"/>
+      <c r="D27" s="13"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B28" s="24"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="19"/>
+      <c r="B28" s="62"/>
+      <c r="C28" s="62"/>
+      <c r="D28" s="13"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B29" s="25"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="19"/>
+      <c r="B29" s="64"/>
+      <c r="C29" s="64"/>
+      <c r="D29" s="13"/>
     </row>
     <row r="30" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="26" t="s">
+      <c r="A30" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="B30" s="26"/>
-      <c r="C30" s="26"/>
+      <c r="B30" s="65"/>
+      <c r="C30" s="65"/>
     </row>
     <row r="31" spans="1:4" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="27" t="s">
+      <c r="A31" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="B31" s="24" t="s">
+      <c r="B31" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="24"/>
+      <c r="C31" s="62"/>
     </row>
     <row r="32" spans="1:4" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="27" t="s">
+      <c r="A32" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="C32" s="24"/>
-      <c r="D32" s="28"/>
+      <c r="C32" s="62"/>
+      <c r="D32" s="18"/>
     </row>
     <row r="33" spans="1:4" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="27" t="s">
+      <c r="A33" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="B33" s="24" t="s">
+      <c r="B33" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="C33" s="24"/>
-      <c r="D33" s="28"/>
+      <c r="C33" s="62"/>
+      <c r="D33" s="18"/>
     </row>
     <row r="34" spans="1:4" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="27" t="s">
+      <c r="A34" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="B34" s="24" t="s">
+      <c r="B34" s="62" t="s">
         <v>51</v>
       </c>
-      <c r="C34" s="24"/>
-      <c r="D34" s="28"/>
+      <c r="C34" s="62"/>
+      <c r="D34" s="18"/>
     </row>
     <row r="35" spans="1:4" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="27" t="s">
+      <c r="A35" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B35" s="24" t="s">
+      <c r="B35" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="C35" s="24"/>
-      <c r="D35" s="28"/>
+      <c r="C35" s="62"/>
+      <c r="D35" s="18"/>
     </row>
     <row r="36" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="27" t="s">
+      <c r="A36" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="B36" s="24" t="s">
+      <c r="B36" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="C36" s="24"/>
+      <c r="C36" s="62"/>
     </row>
     <row r="37" spans="1:4" ht="50.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="29" t="s">
+      <c r="A37" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="B37" s="24" t="s">
+      <c r="B37" s="62" t="s">
         <v>57</v>
       </c>
-      <c r="C37" s="24"/>
-      <c r="D37" s="28"/>
+      <c r="C37" s="62"/>
+      <c r="D37" s="18"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A38" s="16" t="s">
+      <c r="A38" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="B38" s="76" t="s">
+      <c r="B38" s="61" t="s">
         <v>235</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ZVn0jUEPzoIfUl3dD37kz0FvIeao98JpHZ24dDEy4TFce3EvEoXpwnk6sDPy84CbLuhSBCpIhjB+cNGhgWZsTA==" saltValue="O//HFjAWcWe0uVxT8laXhw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="DlaS1hCWqH0kVlgwnjCBh1rObj79vG6hTzGVvmohc9aXVclnpMVajncjpdBQqIFSjpIpQwRHZf42BDwIhGnZ3g==" saltValue="X78TL18obxyFCpO2AtK8Hw==" spinCount="100000" sheet="1"/>
   <mergeCells count="11">
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
@@ -2393,343 +2389,343 @@
   <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="30" style="16" customWidth="1"/>
-    <col min="2" max="2" width="22.625" style="16" customWidth="1"/>
-    <col min="3" max="3" width="40.125" style="16" customWidth="1"/>
-    <col min="4" max="4" width="34.875" style="16" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12" style="16" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="17"/>
+    <col min="1" max="1" width="30" style="10" customWidth="1"/>
+    <col min="2" max="2" width="22.625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="40.125" style="10" customWidth="1"/>
+    <col min="4" max="4" width="34.875" style="10" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="10" customWidth="1"/>
+    <col min="6" max="6" width="12" style="10" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
     </row>
     <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F3" s="18"/>
+      <c r="F3" s="12"/>
     </row>
     <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="32" t="str">
+      <c r="B4" s="21" t="str">
         <f>IF(入力!B17="DC → 会社退職金","企業型DC",IF(入力!B17="会社退職金 → DC","会社退職金","要確認"))</f>
         <v>企業型DC</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
     </row>
     <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="33">
+      <c r="B5" s="22">
         <f>IF(OR(入力!B8="",入力!B12=""),"",MIN(入力!B8,入力!B12))</f>
         <v>46172</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C5" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
     </row>
     <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="33">
+      <c r="B6" s="22">
         <f>IF(OR(入力!B8="",入力!B12=""),"",MAX(入力!B8,入力!B12))</f>
         <v>49459</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
     </row>
     <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="17">
         <f>IF(B4="企業型DC",入力!B13,IF(B4="会社退職金",入力!B9,""))</f>
         <v>10000000</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
     </row>
     <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="17">
         <f>IF(B4="企業型DC",入力!B21,IF(B4="会社退職金",入力!B19,""))</f>
         <v>15</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
     </row>
     <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="17">
         <f>IF(B4="企業型DC",入力!B22,IF(B4="会社退職金",入力!B20,""))</f>
         <v>6000000</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
     </row>
     <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="B10" s="23" t="str">
+      <c r="B10" s="17" t="str">
         <f>IF(B7="","",IF(B7&lt;B9,"該当","非該当"))</f>
         <v>非該当</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
     </row>
     <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B11" s="17">
         <f>IF(B10="該当",ROUNDDOWN(IF(B7&lt;=8000000,B7/400000,(B7-8000000)/700000+20),0),B8)</f>
         <v>15</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="F11" s="19"/>
+      <c r="F11" s="13"/>
     </row>
     <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B12" s="17">
         <f>入力!B23</f>
         <v>9</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
     </row>
     <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="B13" s="23" t="str">
+      <c r="B13" s="17" t="str">
         <f>IF(OR(B5="",B6="",B12=""),"",IF(YEARFRAC(B5,B6,1)&lt;=B12,"対象","対象外"))</f>
         <v>対象外</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19" t="s">
+      <c r="E13" s="13"/>
+      <c r="F13" s="13" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B14" s="17">
         <f>IF(B13="対象","要計算（開始日・終了日で算定）",IF(B13="対象外",0,"要確認"))</f>
         <v>0</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="13" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="17">
         <f>IF(B14=0,IF(B4="企業型DC",入力!B22,入力!B20),"要計算")</f>
         <v>6000000</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="F15" s="13" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="10" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="10" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="B19" s="69" t="s">
         <v>98</v>
       </c>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
+      <c r="C19" s="67"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="67"/>
+      <c r="F19" s="67"/>
     </row>
     <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
+      <c r="B20" s="67"/>
+      <c r="C20" s="67"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="67"/>
+      <c r="F20" s="67"/>
     </row>
     <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
+      <c r="B21" s="67"/>
+      <c r="C21" s="67"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="67"/>
     </row>
     <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="35" t="s">
+      <c r="A23" s="66" t="s">
         <v>99</v>
       </c>
-      <c r="B23" s="31"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="67"/>
     </row>
     <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="B24" s="34" t="s">
+      <c r="B24" s="69" t="s">
         <v>101</v>
       </c>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
+      <c r="C24" s="67"/>
+      <c r="D24" s="67"/>
     </row>
     <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="B25" s="34" t="s">
+      <c r="B25" s="69" t="s">
         <v>103</v>
       </c>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
     </row>
     <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="19" t="s">
+      <c r="A26" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="34" t="s">
+      <c r="B26" s="69" t="s">
         <v>104</v>
       </c>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
+      <c r="C26" s="67"/>
+      <c r="D26" s="67"/>
     </row>
     <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
@@ -2753,195 +2749,195 @@
   <dimension ref="A1:AQ25"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9" style="16" customWidth="1"/>
-    <col min="2" max="2" width="13" style="16" customWidth="1"/>
-    <col min="3" max="3" width="15" style="16" customWidth="1"/>
-    <col min="4" max="4" width="14" style="16" customWidth="1"/>
-    <col min="5" max="5" width="16" style="16" customWidth="1"/>
-    <col min="6" max="6" width="20" style="16" customWidth="1"/>
-    <col min="7" max="7" width="16.875" style="16" customWidth="1"/>
-    <col min="8" max="8" width="18" style="16" customWidth="1"/>
-    <col min="9" max="10" width="16" style="16" customWidth="1"/>
-    <col min="11" max="12" width="11" style="16" customWidth="1"/>
-    <col min="13" max="14" width="15" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12" style="16" customWidth="1"/>
-    <col min="16" max="19" width="16" style="16" customWidth="1"/>
-    <col min="20" max="20" width="14" style="16" customWidth="1"/>
-    <col min="21" max="21" width="16" style="16" customWidth="1"/>
-    <col min="22" max="22" width="12" style="16" customWidth="1"/>
-    <col min="23" max="23" width="16" style="16" customWidth="1"/>
-    <col min="24" max="26" width="14" style="16" customWidth="1"/>
-    <col min="27" max="28" width="16" style="16" customWidth="1"/>
-    <col min="29" max="29" width="20" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="35" width="14" style="16" customWidth="1"/>
-    <col min="36" max="36" width="16" style="16" customWidth="1"/>
-    <col min="37" max="38" width="14" style="16" customWidth="1"/>
-    <col min="39" max="39" width="18" style="16" customWidth="1"/>
-    <col min="40" max="40" width="16" style="17" customWidth="1"/>
-    <col min="41" max="41" width="11.75" style="17" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="11.125" style="17" customWidth="1"/>
-    <col min="43" max="43" width="12.75" style="17" customWidth="1"/>
-    <col min="44" max="16384" width="9" style="17"/>
+    <col min="1" max="1" width="9" style="10" customWidth="1"/>
+    <col min="2" max="2" width="13" style="10" customWidth="1"/>
+    <col min="3" max="3" width="15" style="10" customWidth="1"/>
+    <col min="4" max="4" width="14" style="10" customWidth="1"/>
+    <col min="5" max="5" width="16" style="10" customWidth="1"/>
+    <col min="6" max="6" width="20" style="10" customWidth="1"/>
+    <col min="7" max="7" width="16.875" style="10" customWidth="1"/>
+    <col min="8" max="8" width="18" style="10" customWidth="1"/>
+    <col min="9" max="10" width="16" style="10" customWidth="1"/>
+    <col min="11" max="12" width="11" style="10" customWidth="1"/>
+    <col min="13" max="14" width="15" style="10" customWidth="1"/>
+    <col min="15" max="15" width="12" style="10" customWidth="1"/>
+    <col min="16" max="19" width="16" style="10" customWidth="1"/>
+    <col min="20" max="20" width="14" style="10" customWidth="1"/>
+    <col min="21" max="21" width="16" style="10" customWidth="1"/>
+    <col min="22" max="22" width="12" style="10" customWidth="1"/>
+    <col min="23" max="23" width="16" style="10" customWidth="1"/>
+    <col min="24" max="26" width="14" style="10" customWidth="1"/>
+    <col min="27" max="28" width="16" style="10" customWidth="1"/>
+    <col min="29" max="29" width="20" style="10" customWidth="1"/>
+    <col min="30" max="30" width="12" style="10" customWidth="1"/>
+    <col min="31" max="35" width="14" style="10" customWidth="1"/>
+    <col min="36" max="36" width="16" style="10" customWidth="1"/>
+    <col min="37" max="38" width="14" style="10" customWidth="1"/>
+    <col min="39" max="39" width="18" style="10" customWidth="1"/>
+    <col min="40" max="40" width="16" style="11" customWidth="1"/>
+    <col min="41" max="41" width="11.75" style="11" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="11.125" style="11" customWidth="1"/>
+    <col min="43" max="43" width="12.75" style="11" customWidth="1"/>
+    <col min="44" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="24" x14ac:dyDescent="0.5">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="70" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
     </row>
     <row r="2" spans="1:43" x14ac:dyDescent="0.4">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17" t="s">
+      <c r="B2" s="11"/>
+      <c r="C2" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="AN2" s="16"/>
+      <c r="AN2" s="10"/>
     </row>
     <row r="3" spans="1:43" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="23" t="s">
         <v>219</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="37" t="s">
+      <c r="D3" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="E3" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="37" t="s">
+      <c r="G3" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="37" t="s">
+      <c r="H3" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="I3" s="37" t="s">
+      <c r="I3" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="J3" s="37" t="s">
+      <c r="J3" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="K3" s="37" t="s">
+      <c r="K3" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="L3" s="38" t="s">
+      <c r="L3" s="24" t="s">
         <v>227</v>
       </c>
-      <c r="M3" s="38" t="s">
+      <c r="M3" s="24" t="s">
         <v>221</v>
       </c>
-      <c r="N3" s="38" t="s">
+      <c r="N3" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="O3" s="38" t="s">
+      <c r="O3" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="P3" s="38" t="s">
+      <c r="P3" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="Q3" s="38" t="s">
+      <c r="Q3" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="R3" s="38" t="s">
+      <c r="R3" s="24" t="s">
         <v>224</v>
       </c>
-      <c r="S3" s="38" t="s">
+      <c r="S3" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="T3" s="38" t="s">
+      <c r="T3" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="U3" s="38" t="s">
+      <c r="U3" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="V3" s="38" t="s">
+      <c r="V3" s="24" t="s">
         <v>228</v>
       </c>
-      <c r="W3" s="38" t="s">
+      <c r="W3" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="X3" s="38" t="s">
+      <c r="X3" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="Y3" s="38" t="s">
+      <c r="Y3" s="24" t="s">
         <v>229</v>
       </c>
-      <c r="Z3" s="38" t="s">
+      <c r="Z3" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="AA3" s="38" t="s">
+      <c r="AA3" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="AB3" s="38" t="s">
+      <c r="AB3" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="AC3" s="38" t="s">
+      <c r="AC3" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="AD3" s="38" t="s">
+      <c r="AD3" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="AE3" s="38" t="s">
+      <c r="AE3" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="AF3" s="38" t="s">
+      <c r="AF3" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="AG3" s="38" t="s">
+      <c r="AG3" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="AH3" s="38" t="s">
+      <c r="AH3" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="AI3" s="38" t="s">
+      <c r="AI3" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="AJ3" s="38" t="s">
+      <c r="AJ3" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="AK3" s="38" t="s">
+      <c r="AK3" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="AL3" s="38" t="s">
+      <c r="AL3" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="AM3" s="38" t="s">
+      <c r="AM3" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="AN3" s="38" t="s">
+      <c r="AN3" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="AO3" s="38" t="s">
+      <c r="AO3" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="AP3" s="38" t="s">
+      <c r="AP3" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="AQ3" s="38" t="s">
+      <c r="AQ3" s="24" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="39">
+      <c r="A4" s="25">
         <v>1</v>
       </c>
       <c r="B4" s="5">
@@ -2950,35 +2946,35 @@
       <c r="C4" s="5">
         <v>47664</v>
       </c>
-      <c r="D4" s="40">
+      <c r="D4" s="26">
         <f>入力!$B$8</f>
         <v>49459</v>
       </c>
-      <c r="E4" s="41">
+      <c r="E4" s="27">
         <f>入力!$B$13</f>
         <v>10000000</v>
       </c>
-      <c r="F4" s="41">
+      <c r="F4" s="27">
         <f>入力!$B$9</f>
         <v>1000000</v>
       </c>
-      <c r="G4" s="42" t="str">
+      <c r="G4" s="28" t="str">
         <f t="shared" ref="G4:G13" si="0">IF(OR(C4="",D4=""),"",IF(YEAR(C4)=YEAR(D4),"同年受取",IF(C4&lt;D4,"DC → 会社退職金","会社退職金 → DC")))</f>
         <v>DC → 会社退職金</v>
       </c>
-      <c r="H4" s="42">
+      <c r="H4" s="28">
         <f t="shared" ref="H4:H13" si="1">IF(OR(G4="同年受取",G4=""),"",IF(G4="DC → 会社退職金",9,19))</f>
         <v>9</v>
       </c>
-      <c r="I4" s="42" t="str">
+      <c r="I4" s="28" t="str">
         <f t="shared" ref="I4:I13" si="2">IF(G4="同年受取","同年合算",IF(G4="","",IF(AND(MIN(C4,D4)&lt;DATE(YEAR(MAX(C4,D4)),1,1),MIN(C4,D4)&gt;=DATE(YEAR(MAX(C4,D4))-H4,1,1)),"対象","対象外")))</f>
         <v>対象</v>
       </c>
-      <c r="J4" s="41">
+      <c r="J4" s="27">
         <f t="shared" ref="J4:J13" si="3">IF(G4="同年受取","",IF(G4="DC → 会社退職金",E4,IF(G4="会社退職金 → DC",F4,"")))</f>
         <v>10000000</v>
       </c>
-      <c r="K4" s="41">
+      <c r="K4" s="27">
         <f>IF(G4="同年受取","",
  IF(G4="DC → 会社退職金",
    _xlfn.LET(
@@ -2995,11 +2991,11 @@
  "")))</f>
         <v>3600000</v>
       </c>
-      <c r="L4" s="43" t="str">
+      <c r="L4" s="29" t="str">
         <f t="shared" ref="L4:L13" si="4">IF(OR(J4="",K4=""),"",IF(J4&lt;K4,"該当","非該当"))</f>
         <v>非該当</v>
       </c>
-      <c r="M4" s="44">
+      <c r="M4" s="30">
         <f>_xlfn.LET(
  _xlpm.前退,J4,
  _xlpm.前控,K4,
@@ -3026,11 +3022,11 @@
 )</f>
         <v>9</v>
       </c>
-      <c r="N4" s="45">
+      <c r="N4" s="31">
         <f>IF(G4="同年受取","",IF(I4&lt;&gt;"対象","",MAX(IF(G4="DC → 会社退職金",入力!$B$10,入力!$B$6),IF(G4="DC → 会社退職金",入力!$B$6,入力!$B$10))))</f>
         <v>44652</v>
       </c>
-      <c r="O4" s="45">
+      <c r="O4" s="31">
         <f>_xlfn.LET(
   _xlpm.受取順,G4,
   _xlpm.対象,I4,
@@ -3073,7 +3069,7 @@
 )</f>
         <v>47664</v>
       </c>
-      <c r="P4" s="44">
+      <c r="P4" s="30">
         <f t="shared" ref="P4:P13" si="5">_xlfn.LET(
   _xlpm.重複開始,N4,
   _xlpm.重複終了,O4,
@@ -3089,7 +3085,7 @@
 )</f>
         <v>8</v>
       </c>
-      <c r="Q4" s="43">
+      <c r="Q4" s="29">
         <f>IF(G4="同年受取","",
 _xlfn.LET(
 _xlpm.受取順,G4,
@@ -3112,7 +3108,7 @@
 ))</f>
         <v>23700000</v>
       </c>
-      <c r="R4" s="43">
+      <c r="R4" s="29">
         <f>IF(G4="同年受取","",
  _xlfn.LET(
   _xlpm.受取順,G4,
@@ -3151,67 +3147,67 @@
 )</f>
         <v>3600000</v>
       </c>
-      <c r="S4" s="43">
+      <c r="S4" s="29">
         <f t="shared" ref="S4:S13" si="6">IF(G4="同年受取","",IF(OR(G4="",G4="同日受取：要確認"),"",ROUNDDOWN(MAX(0,(F4-Q4)/2),-3)))</f>
         <v>0</v>
       </c>
-      <c r="T4" s="43">
+      <c r="T4" s="29">
         <f t="shared" ref="T4:T13" si="7">IF(G4="同年受取","",IF(OR(G4="",G4="同日受取：要確認"),"",ROUNDDOWN(MAX(0,(E4-R4)/2),-3)))</f>
         <v>3200000</v>
       </c>
-      <c r="U4" s="46">
+      <c r="U4" s="32">
         <f>IF(OR(G4="同年受取",S4=""),"",VLOOKUP(S4,税率表!$A$2:$C$8,2,TRUE))</f>
         <v>0.05</v>
       </c>
-      <c r="V4" s="43">
+      <c r="V4" s="29">
         <f>IF(U4="","",VLOOKUP(S4,税率表!$A$2:$C$8,3,TRUE))</f>
         <v>0</v>
       </c>
-      <c r="W4" s="43">
+      <c r="W4" s="29">
         <f t="shared" ref="W4:W13" si="8">IF(U4="","",ROUNDDOWN(MAX(0,S4*U4-V4)*1.021,0))</f>
         <v>0</v>
       </c>
-      <c r="X4" s="46">
+      <c r="X4" s="32">
         <f>IF(OR(G4="同年受取",T4=""),"",VLOOKUP(T4,税率表!$A$2:$C$8,2,TRUE))</f>
         <v>0.1</v>
       </c>
-      <c r="Y4" s="43">
+      <c r="Y4" s="29">
         <f>IF(X4="","",VLOOKUP(T4,税率表!$A$2:$C$8,3,TRUE))</f>
         <v>97500</v>
       </c>
-      <c r="Z4" s="43">
+      <c r="Z4" s="29">
         <f t="shared" ref="Z4:Z13" si="9">IF(X4="","",ROUNDDOWN(MAX(0,T4*X4-Y4)*1.021,0))</f>
         <v>227172</v>
       </c>
-      <c r="AA4" s="43">
+      <c r="AA4" s="29">
         <f t="shared" ref="AA4:AA13" si="10">IF(G4="同年受取","",IF(S4="","",ROUNDDOWN(S4*10%,0)))</f>
         <v>0</v>
       </c>
-      <c r="AB4" s="43">
+      <c r="AB4" s="29">
         <f t="shared" ref="AB4:AB13" si="11">IF(G4="同年受取","",IF(T4="","",ROUNDDOWN(T4*10%,0)))</f>
         <v>320000</v>
       </c>
-      <c r="AC4" s="43">
+      <c r="AC4" s="29">
         <f t="shared" ref="AC4:AC13" si="12">IF(G4="同年受取","",IF(OR(W4="",Z4=""),"",SUM(W4,Z4,AA4,AB4)))</f>
         <v>547172</v>
       </c>
-      <c r="AD4" s="43">
+      <c r="AD4" s="29">
         <f t="shared" ref="AD4:AD13" si="13">IF(G4="同年受取","",IF(AC4="","",E4+F4-AC4))</f>
         <v>10452828</v>
       </c>
-      <c r="AE4" s="47" t="str">
+      <c r="AE4" s="33" t="str">
         <f t="shared" ref="AE4:AE13" si="14">IF(G4="同年受取","No.2735：同年の退職手当等を合算し、2制度の勤続期間を統合して退職所得控除額を計算",IF(I4="対象","No.2732：確認期間→前の金額/控除→換算年数→重複年度→後の控除調整→課税退職所得→税額",IF(G4="","",IF(I4="対象外","No.2732：確認期間外→重複調整なし→通常控除→課税退職所得→税額",""))))</f>
         <v>No.2732：確認期間→前の金額/控除→換算年数→重複年度→後の控除調整→課税退職所得→税額</v>
       </c>
-      <c r="AF4" s="47">
+      <c r="AF4" s="33">
         <f t="shared" ref="AF4:AF13" si="15">IF(OR(J4="",K4="",G4="同年受取"),"",ROUNDDOWN(IF(J4&lt;=8000000,J4/400000,(J4-8000000)/700000+20),0))</f>
         <v>22</v>
       </c>
-      <c r="AG4" s="47">
+      <c r="AG4" s="33">
         <f>IF(OR(J4="",K4="",G4="同年受取"),"",IF(J4&lt;K4,AF4,IF(G4="DC → 会社退職金",入力!$B$21,入力!$B$19)))</f>
         <v>15</v>
       </c>
-      <c r="AH4" s="48" t="str">
+      <c r="AH4" s="34" t="str">
         <f>IF(G4&lt;&gt;"同年受取","",_xlfn.LET(
 _xlpm.A開始,入力!$B$6,
 _xlpm.A終了,入力!$B$7,
@@ -3231,45 +3227,45 @@
 ))</f>
         <v/>
       </c>
-      <c r="AI4" s="49" t="str">
+      <c r="AI4" s="35" t="str">
         <f t="shared" ref="AI4:AI13" si="16">IF(G4&lt;&gt;"同年受取","",IF(AH4&lt;=20,MAX(400000*AH4,800000),8000000+700000*(AH4-20)))</f>
         <v/>
       </c>
-      <c r="AJ4" s="49" t="str">
+      <c r="AJ4" s="35" t="str">
         <f t="shared" ref="AJ4:AJ13" si="17">IF(G4&lt;&gt;"同年受取","",MAX(0,FLOOR((E4+F4-AI4)/2,1000)))</f>
         <v/>
       </c>
-      <c r="AK4" s="50" t="str">
+      <c r="AK4" s="36" t="str">
         <f t="shared" ref="AK4:AK13" si="18">IF(G4&lt;&gt;"同年受取","",VLOOKUP(AJ4,tabletax,3,TRUE))</f>
         <v/>
       </c>
-      <c r="AL4" s="49" t="str">
+      <c r="AL4" s="35" t="str">
         <f t="shared" ref="AL4:AL13" si="19">IF(G4&lt;&gt;"同年受取","",VLOOKUP(AJ4,tabletax,4,TRUE))</f>
         <v/>
       </c>
-      <c r="AM4" s="49" t="str">
+      <c r="AM4" s="35" t="str">
         <f t="shared" ref="AM4:AM13" si="20">IF(G4&lt;&gt;"同年受取","",FLOOR((AJ4*AK4-AL4)*1.021,1))</f>
         <v/>
       </c>
-      <c r="AN4" s="49" t="str">
+      <c r="AN4" s="35" t="str">
         <f t="shared" ref="AN4:AN13" si="21">IF(G4&lt;&gt;"同年受取","",FLOOR(AJ4*0.1,100))</f>
         <v/>
       </c>
-      <c r="AO4" s="49" t="str">
+      <c r="AO4" s="35" t="str">
         <f t="shared" ref="AO4:AO13" si="22">IF(G4&lt;&gt;"同年受取","",AM4+AN4)</f>
         <v/>
       </c>
-      <c r="AP4" s="49" t="str">
+      <c r="AP4" s="35" t="str">
         <f t="shared" ref="AP4:AP13" si="23">IF(G4&lt;&gt;"同年受取","",IF(AM4="","",E4+F4-AO4))</f>
         <v/>
       </c>
-      <c r="AQ4" s="49">
+      <c r="AQ4" s="35">
         <f t="shared" ref="AQ4:AQ13" si="24">IF(AD4&lt;&gt;"",AD4,IF(AP4&lt;&gt;"",AP4))</f>
         <v>10452828</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="39">
+      <c r="A5" s="25">
         <v>2</v>
       </c>
       <c r="B5" s="5">
@@ -3278,35 +3274,35 @@
       <c r="C5" s="5">
         <v>48029</v>
       </c>
-      <c r="D5" s="40">
+      <c r="D5" s="26">
         <f>入力!$B$8</f>
         <v>49459</v>
       </c>
-      <c r="E5" s="41">
+      <c r="E5" s="27">
         <f>入力!$B$13</f>
         <v>10000000</v>
       </c>
-      <c r="F5" s="41">
+      <c r="F5" s="27">
         <f>入力!$B$9</f>
         <v>1000000</v>
       </c>
-      <c r="G5" s="42" t="str">
+      <c r="G5" s="28" t="str">
         <f t="shared" si="0"/>
         <v>DC → 会社退職金</v>
       </c>
-      <c r="H5" s="42">
+      <c r="H5" s="28">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="I5" s="42" t="str">
+      <c r="I5" s="28" t="str">
         <f t="shared" si="2"/>
         <v>対象</v>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="27">
         <f t="shared" si="3"/>
         <v>10000000</v>
       </c>
-      <c r="K5" s="41">
+      <c r="K5" s="27">
         <f>IF(G5="同年受取","",
  IF(G5="DC → 会社退職金",
    _xlfn.LET(
@@ -3323,11 +3319,11 @@
  "")))</f>
         <v>4000000</v>
       </c>
-      <c r="L5" s="43" t="str">
+      <c r="L5" s="29" t="str">
         <f t="shared" si="4"/>
         <v>非該当</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="30">
         <f>_xlfn.LET(
  _xlpm.前判定,L5,
  _xlpm.前退,J5,
@@ -3355,11 +3351,11 @@
 )</f>
         <v>10</v>
       </c>
-      <c r="N5" s="45">
+      <c r="N5" s="31">
         <f>IF(G5="同年受取","",IF(I5&lt;&gt;"対象","",MAX(IF(G5="DC → 会社退職金",入力!$B$10,入力!$B$6),IF(G5="DC → 会社退職金",入力!$B$6,入力!$B$10))))</f>
         <v>44652</v>
       </c>
-      <c r="O5" s="45">
+      <c r="O5" s="31">
         <f>_xlfn.LET(
   _xlpm.受取順,G5,
   _xlpm.対象,I5,
@@ -3402,11 +3398,11 @@
 )</f>
         <v>48029</v>
       </c>
-      <c r="P5" s="44">
+      <c r="P5" s="30">
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
-      <c r="Q5" s="43">
+      <c r="Q5" s="29">
         <f>IF(G5="同年受取","",
 _xlfn.LET(
 _xlpm.受取順,G5,
@@ -3429,7 +3425,7 @@
 ))</f>
         <v>23300000</v>
       </c>
-      <c r="R5" s="43">
+      <c r="R5" s="29">
         <f>IF(G5="同年受取","",
  _xlfn.LET(
   _xlpm.受取順,G5,
@@ -3468,67 +3464,67 @@
 )</f>
         <v>4000000</v>
       </c>
-      <c r="S5" s="43">
+      <c r="S5" s="29">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T5" s="43">
+      <c r="T5" s="29">
         <f t="shared" si="7"/>
         <v>3000000</v>
       </c>
-      <c r="U5" s="46">
+      <c r="U5" s="32">
         <f>IF(OR(G5="同年受取",S5=""),"",VLOOKUP(S5,税率表!$A$2:$C$8,2,TRUE))</f>
         <v>0.05</v>
       </c>
-      <c r="V5" s="43">
+      <c r="V5" s="29">
         <f>IF(U5="","",VLOOKUP(S5,税率表!$A$2:$C$8,3,TRUE))</f>
         <v>0</v>
       </c>
-      <c r="W5" s="43">
+      <c r="W5" s="29">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X5" s="46">
+      <c r="X5" s="32">
         <f>IF(OR(G5="同年受取",T5=""),"",VLOOKUP(T5,税率表!$A$2:$C$8,2,TRUE))</f>
         <v>0.1</v>
       </c>
-      <c r="Y5" s="43">
+      <c r="Y5" s="29">
         <f>IF(X5="","",VLOOKUP(T5,税率表!$A$2:$C$8,3,TRUE))</f>
         <v>97500</v>
       </c>
-      <c r="Z5" s="43">
+      <c r="Z5" s="29">
         <f t="shared" si="9"/>
         <v>206752</v>
       </c>
-      <c r="AA5" s="43">
+      <c r="AA5" s="29">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AB5" s="43">
+      <c r="AB5" s="29">
         <f t="shared" si="11"/>
         <v>300000</v>
       </c>
-      <c r="AC5" s="43">
+      <c r="AC5" s="29">
         <f t="shared" si="12"/>
         <v>506752</v>
       </c>
-      <c r="AD5" s="43">
+      <c r="AD5" s="29">
         <f t="shared" si="13"/>
         <v>10493248</v>
       </c>
-      <c r="AE5" s="47" t="str">
+      <c r="AE5" s="33" t="str">
         <f t="shared" si="14"/>
         <v>No.2732：確認期間→前の金額/控除→換算年数→重複年度→後の控除調整→課税退職所得→税額</v>
       </c>
-      <c r="AF5" s="47">
+      <c r="AF5" s="33">
         <f t="shared" si="15"/>
         <v>22</v>
       </c>
-      <c r="AG5" s="47">
+      <c r="AG5" s="33">
         <f>IF(OR(J5="",K5="",G5="同年受取"),"",IF(J5&lt;K5,AF5,IF(G5="DC → 会社退職金",入力!$B$21,入力!$B$19)))</f>
         <v>15</v>
       </c>
-      <c r="AH5" s="48" t="str">
+      <c r="AH5" s="34" t="str">
         <f>IF(G5&lt;&gt;"同年受取","",_xlfn.LET(
 _xlpm.A開始,入力!$B$6,
 _xlpm.A終了,入力!$B$7,
@@ -3548,45 +3544,45 @@
 ))</f>
         <v/>
       </c>
-      <c r="AI5" s="49" t="str">
+      <c r="AI5" s="35" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AJ5" s="49" t="str">
+      <c r="AJ5" s="35" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AK5" s="50" t="str">
+      <c r="AK5" s="36" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AL5" s="49" t="str">
+      <c r="AL5" s="35" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AM5" s="49" t="str">
+      <c r="AM5" s="35" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN5" s="49" t="str">
+      <c r="AN5" s="35" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AO5" s="49" t="str">
+      <c r="AO5" s="35" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AP5" s="49" t="str">
+      <c r="AP5" s="35" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="AQ5" s="49">
+      <c r="AQ5" s="35">
         <f t="shared" si="24"/>
         <v>10493248</v>
       </c>
     </row>
     <row r="6" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="39">
+      <c r="A6" s="25">
         <v>3</v>
       </c>
       <c r="B6" s="5">
@@ -3595,35 +3591,35 @@
       <c r="C6" s="5">
         <v>48395</v>
       </c>
-      <c r="D6" s="40">
+      <c r="D6" s="26">
         <f>入力!$B$8</f>
         <v>49459</v>
       </c>
-      <c r="E6" s="41">
+      <c r="E6" s="27">
         <f>入力!$B$13</f>
         <v>10000000</v>
       </c>
-      <c r="F6" s="41">
+      <c r="F6" s="27">
         <f>入力!$B$9</f>
         <v>1000000</v>
       </c>
-      <c r="G6" s="42" t="str">
+      <c r="G6" s="28" t="str">
         <f t="shared" si="0"/>
         <v>DC → 会社退職金</v>
       </c>
-      <c r="H6" s="42">
+      <c r="H6" s="28">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="I6" s="42" t="str">
+      <c r="I6" s="28" t="str">
         <f t="shared" si="2"/>
         <v>対象</v>
       </c>
-      <c r="J6" s="41">
+      <c r="J6" s="27">
         <f t="shared" si="3"/>
         <v>10000000</v>
       </c>
-      <c r="K6" s="41">
+      <c r="K6" s="27">
         <f>IF(G6="同年受取","",
  IF(G6="DC → 会社退職金",
    _xlfn.LET(
@@ -3640,11 +3636,11 @@
  "")))</f>
         <v>4400000</v>
       </c>
-      <c r="L6" s="43" t="str">
+      <c r="L6" s="29" t="str">
         <f t="shared" si="4"/>
         <v>非該当</v>
       </c>
-      <c r="M6" s="44">
+      <c r="M6" s="30">
         <f>_xlfn.LET(
  _xlpm.前判定,L6,
  _xlpm.前退,J6,
@@ -3672,11 +3668,11 @@
 )</f>
         <v>11</v>
       </c>
-      <c r="N6" s="45">
+      <c r="N6" s="31">
         <f>IF(G6="同年受取","",IF(I6&lt;&gt;"対象","",MAX(IF(G6="DC → 会社退職金",入力!$B$10,入力!$B$6),IF(G6="DC → 会社退職金",入力!$B$6,入力!$B$10))))</f>
         <v>44652</v>
       </c>
-      <c r="O6" s="45">
+      <c r="O6" s="31">
         <f>_xlfn.LET(
   _xlpm.受取順,G6,
   _xlpm.対象,I6,
@@ -3719,11 +3715,11 @@
 )</f>
         <v>48395</v>
       </c>
-      <c r="P6" s="44">
+      <c r="P6" s="30">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="Q6" s="43">
+      <c r="Q6" s="29">
         <f>IF(G6="同年受取","",
 _xlfn.LET(
 _xlpm.受取順,G6,
@@ -3746,7 +3742,7 @@
 ))</f>
         <v>22900000</v>
       </c>
-      <c r="R6" s="43">
+      <c r="R6" s="29">
         <f>IF(G6="同年受取","",
  _xlfn.LET(
   _xlpm.受取順,G6,
@@ -3785,67 +3781,67 @@
 )</f>
         <v>4400000</v>
       </c>
-      <c r="S6" s="43">
+      <c r="S6" s="29">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T6" s="43">
+      <c r="T6" s="29">
         <f t="shared" si="7"/>
         <v>2800000</v>
       </c>
-      <c r="U6" s="46">
+      <c r="U6" s="32">
         <f>IF(OR(G6="同年受取",S6=""),"",VLOOKUP(S6,税率表!$A$2:$C$8,2,TRUE))</f>
         <v>0.05</v>
       </c>
-      <c r="V6" s="43">
+      <c r="V6" s="29">
         <f>IF(U6="","",VLOOKUP(S6,税率表!$A$2:$C$8,3,TRUE))</f>
         <v>0</v>
       </c>
-      <c r="W6" s="43">
+      <c r="W6" s="29">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X6" s="46">
+      <c r="X6" s="32">
         <f>IF(OR(G6="同年受取",T6=""),"",VLOOKUP(T6,税率表!$A$2:$C$8,2,TRUE))</f>
         <v>0.1</v>
       </c>
-      <c r="Y6" s="43">
+      <c r="Y6" s="29">
         <f>IF(X6="","",VLOOKUP(T6,税率表!$A$2:$C$8,3,TRUE))</f>
         <v>97500</v>
       </c>
-      <c r="Z6" s="43">
+      <c r="Z6" s="29">
         <f t="shared" si="9"/>
         <v>186332</v>
       </c>
-      <c r="AA6" s="43">
+      <c r="AA6" s="29">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AB6" s="43">
+      <c r="AB6" s="29">
         <f t="shared" si="11"/>
         <v>280000</v>
       </c>
-      <c r="AC6" s="43">
+      <c r="AC6" s="29">
         <f t="shared" si="12"/>
         <v>466332</v>
       </c>
-      <c r="AD6" s="43">
+      <c r="AD6" s="29">
         <f t="shared" si="13"/>
         <v>10533668</v>
       </c>
-      <c r="AE6" s="47" t="str">
+      <c r="AE6" s="33" t="str">
         <f t="shared" si="14"/>
         <v>No.2732：確認期間→前の金額/控除→換算年数→重複年度→後の控除調整→課税退職所得→税額</v>
       </c>
-      <c r="AF6" s="47">
+      <c r="AF6" s="33">
         <f t="shared" si="15"/>
         <v>22</v>
       </c>
-      <c r="AG6" s="47">
+      <c r="AG6" s="33">
         <f>IF(OR(J6="",K6="",G6="同年受取"),"",IF(J6&lt;K6,AF6,IF(G6="DC → 会社退職金",入力!$B$21,入力!$B$19)))</f>
         <v>15</v>
       </c>
-      <c r="AH6" s="48" t="str">
+      <c r="AH6" s="34" t="str">
         <f>IF(G6&lt;&gt;"同年受取","",_xlfn.LET(
 _xlpm.A開始,入力!$B$6,
 _xlpm.A終了,入力!$B$7,
@@ -3865,45 +3861,45 @@
 ))</f>
         <v/>
       </c>
-      <c r="AI6" s="49" t="str">
+      <c r="AI6" s="35" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AJ6" s="49" t="str">
+      <c r="AJ6" s="35" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AK6" s="50" t="str">
+      <c r="AK6" s="36" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AL6" s="49" t="str">
+      <c r="AL6" s="35" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AM6" s="49" t="str">
+      <c r="AM6" s="35" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN6" s="49" t="str">
+      <c r="AN6" s="35" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AO6" s="49" t="str">
+      <c r="AO6" s="35" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AP6" s="49" t="str">
+      <c r="AP6" s="35" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="AQ6" s="49">
+      <c r="AQ6" s="35">
         <f t="shared" si="24"/>
         <v>10533668</v>
       </c>
     </row>
     <row r="7" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="39">
+      <c r="A7" s="25">
         <v>4</v>
       </c>
       <c r="B7" s="5">
@@ -3912,35 +3908,35 @@
       <c r="C7" s="5">
         <v>48760</v>
       </c>
-      <c r="D7" s="40">
+      <c r="D7" s="26">
         <f>入力!$B$8</f>
         <v>49459</v>
       </c>
-      <c r="E7" s="41">
+      <c r="E7" s="27">
         <f>入力!$B$13</f>
         <v>10000000</v>
       </c>
-      <c r="F7" s="41">
+      <c r="F7" s="27">
         <f>入力!$B$9</f>
         <v>1000000</v>
       </c>
-      <c r="G7" s="42" t="str">
+      <c r="G7" s="28" t="str">
         <f t="shared" si="0"/>
         <v>DC → 会社退職金</v>
       </c>
-      <c r="H7" s="42">
+      <c r="H7" s="28">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="I7" s="42" t="str">
+      <c r="I7" s="28" t="str">
         <f t="shared" si="2"/>
         <v>対象</v>
       </c>
-      <c r="J7" s="41">
+      <c r="J7" s="27">
         <f t="shared" si="3"/>
         <v>10000000</v>
       </c>
-      <c r="K7" s="41">
+      <c r="K7" s="27">
         <f>IF(G7="同年受取","",
  IF(G7="DC → 会社退職金",
    _xlfn.LET(
@@ -3957,11 +3953,11 @@
  "")))</f>
         <v>4800000</v>
       </c>
-      <c r="L7" s="43" t="str">
+      <c r="L7" s="29" t="str">
         <f t="shared" si="4"/>
         <v>非該当</v>
       </c>
-      <c r="M7" s="44">
+      <c r="M7" s="30">
         <f>_xlfn.LET(
  _xlpm.前判定,L7,
  _xlpm.前退,J7,
@@ -3989,11 +3985,11 @@
 )</f>
         <v>12</v>
       </c>
-      <c r="N7" s="45">
+      <c r="N7" s="31">
         <f>IF(G7="同年受取","",IF(I7&lt;&gt;"対象","",MAX(IF(G7="DC → 会社退職金",入力!$B$10,入力!$B$6),IF(G7="DC → 会社退職金",入力!$B$6,入力!$B$10))))</f>
         <v>44652</v>
       </c>
-      <c r="O7" s="45">
+      <c r="O7" s="31">
         <f>_xlfn.LET(
   _xlpm.受取順,G7,
   _xlpm.対象,I7,
@@ -4036,11 +4032,11 @@
 )</f>
         <v>48760</v>
       </c>
-      <c r="P7" s="44">
+      <c r="P7" s="30">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="Q7" s="43">
+      <c r="Q7" s="29">
         <f>IF(G7="同年受取","",
 _xlfn.LET(
 _xlpm.受取順,G7,
@@ -4063,7 +4059,7 @@
 ))</f>
         <v>22500000</v>
       </c>
-      <c r="R7" s="43">
+      <c r="R7" s="29">
         <f>IF(G7="同年受取","",
  _xlfn.LET(
   _xlpm.受取順,G7,
@@ -4102,67 +4098,67 @@
 )</f>
         <v>4800000</v>
       </c>
-      <c r="S7" s="43">
+      <c r="S7" s="29">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T7" s="43">
+      <c r="T7" s="29">
         <f t="shared" si="7"/>
         <v>2600000</v>
       </c>
-      <c r="U7" s="46">
+      <c r="U7" s="32">
         <f>IF(OR(G7="同年受取",S7=""),"",VLOOKUP(S7,税率表!$A$2:$C$8,2,TRUE))</f>
         <v>0.05</v>
       </c>
-      <c r="V7" s="43">
+      <c r="V7" s="29">
         <f>IF(U7="","",VLOOKUP(S7,税率表!$A$2:$C$8,3,TRUE))</f>
         <v>0</v>
       </c>
-      <c r="W7" s="43">
+      <c r="W7" s="29">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X7" s="46">
+      <c r="X7" s="32">
         <f>IF(OR(G7="同年受取",T7=""),"",VLOOKUP(T7,税率表!$A$2:$C$8,2,TRUE))</f>
         <v>0.1</v>
       </c>
-      <c r="Y7" s="43">
+      <c r="Y7" s="29">
         <f>IF(X7="","",VLOOKUP(T7,税率表!$A$2:$C$8,3,TRUE))</f>
         <v>97500</v>
       </c>
-      <c r="Z7" s="43">
+      <c r="Z7" s="29">
         <f t="shared" si="9"/>
         <v>165912</v>
       </c>
-      <c r="AA7" s="43">
+      <c r="AA7" s="29">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AB7" s="43">
+      <c r="AB7" s="29">
         <f t="shared" si="11"/>
         <v>260000</v>
       </c>
-      <c r="AC7" s="43">
+      <c r="AC7" s="29">
         <f t="shared" si="12"/>
         <v>425912</v>
       </c>
-      <c r="AD7" s="43">
+      <c r="AD7" s="29">
         <f t="shared" si="13"/>
         <v>10574088</v>
       </c>
-      <c r="AE7" s="47" t="str">
+      <c r="AE7" s="33" t="str">
         <f t="shared" si="14"/>
         <v>No.2732：確認期間→前の金額/控除→換算年数→重複年度→後の控除調整→課税退職所得→税額</v>
       </c>
-      <c r="AF7" s="47">
+      <c r="AF7" s="33">
         <f t="shared" si="15"/>
         <v>22</v>
       </c>
-      <c r="AG7" s="47">
+      <c r="AG7" s="33">
         <f>IF(OR(J7="",K7="",G7="同年受取"),"",IF(J7&lt;K7,AF7,IF(G7="DC → 会社退職金",入力!$B$21,入力!$B$19)))</f>
         <v>15</v>
       </c>
-      <c r="AH7" s="48" t="str">
+      <c r="AH7" s="34" t="str">
         <f>IF(G7&lt;&gt;"同年受取","",_xlfn.LET(
 _xlpm.A開始,入力!$B$6,
 _xlpm.A終了,入力!$B$7,
@@ -4182,45 +4178,45 @@
 ))</f>
         <v/>
       </c>
-      <c r="AI7" s="49" t="str">
+      <c r="AI7" s="35" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AJ7" s="49" t="str">
+      <c r="AJ7" s="35" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AK7" s="50" t="str">
+      <c r="AK7" s="36" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AL7" s="49" t="str">
+      <c r="AL7" s="35" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AM7" s="49" t="str">
+      <c r="AM7" s="35" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN7" s="49" t="str">
+      <c r="AN7" s="35" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AO7" s="49" t="str">
+      <c r="AO7" s="35" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AP7" s="49" t="str">
+      <c r="AP7" s="35" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="AQ7" s="49">
+      <c r="AQ7" s="35">
         <f t="shared" si="24"/>
         <v>10574088</v>
       </c>
     </row>
     <row r="8" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="39">
+      <c r="A8" s="25">
         <v>5</v>
       </c>
       <c r="B8" s="5">
@@ -4229,35 +4225,35 @@
       <c r="C8" s="5">
         <v>49125</v>
       </c>
-      <c r="D8" s="40">
+      <c r="D8" s="26">
         <f>入力!$B$8</f>
         <v>49459</v>
       </c>
-      <c r="E8" s="41">
+      <c r="E8" s="27">
         <f>入力!$B$13</f>
         <v>10000000</v>
       </c>
-      <c r="F8" s="41">
+      <c r="F8" s="27">
         <f>入力!$B$9</f>
         <v>1000000</v>
       </c>
-      <c r="G8" s="42" t="str">
+      <c r="G8" s="28" t="str">
         <f t="shared" si="0"/>
         <v>DC → 会社退職金</v>
       </c>
-      <c r="H8" s="42">
+      <c r="H8" s="28">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="I8" s="42" t="str">
+      <c r="I8" s="28" t="str">
         <f t="shared" si="2"/>
         <v>対象</v>
       </c>
-      <c r="J8" s="41">
+      <c r="J8" s="27">
         <f t="shared" si="3"/>
         <v>10000000</v>
       </c>
-      <c r="K8" s="41">
+      <c r="K8" s="27">
         <f>IF(G8="同年受取","",
  IF(G8="DC → 会社退職金",
    _xlfn.LET(
@@ -4274,11 +4270,11 @@
  "")))</f>
         <v>5200000</v>
       </c>
-      <c r="L8" s="43" t="str">
+      <c r="L8" s="29" t="str">
         <f t="shared" si="4"/>
         <v>非該当</v>
       </c>
-      <c r="M8" s="44">
+      <c r="M8" s="30">
         <f>_xlfn.LET(
  _xlpm.前判定,L8,
  _xlpm.前退,J8,
@@ -4306,11 +4302,11 @@
 )</f>
         <v>13</v>
       </c>
-      <c r="N8" s="45">
+      <c r="N8" s="31">
         <f>IF(G8="同年受取","",IF(I8&lt;&gt;"対象","",MAX(IF(G8="DC → 会社退職金",入力!$B$10,入力!$B$6),IF(G8="DC → 会社退職金",入力!$B$6,入力!$B$10))))</f>
         <v>44652</v>
       </c>
-      <c r="O8" s="45">
+      <c r="O8" s="31">
         <f>_xlfn.LET(
   _xlpm.受取順,G8,
   _xlpm.対象,I8,
@@ -4353,11 +4349,11 @@
 )</f>
         <v>49125</v>
       </c>
-      <c r="P8" s="44">
+      <c r="P8" s="30">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="Q8" s="43">
+      <c r="Q8" s="29">
         <f>IF(G8="同年受取","",
 _xlfn.LET(
 _xlpm.受取順,G8,
@@ -4380,7 +4376,7 @@
 ))</f>
         <v>22100000</v>
       </c>
-      <c r="R8" s="43">
+      <c r="R8" s="29">
         <f>IF(G8="同年受取","",
  _xlfn.LET(
   _xlpm.受取順,G8,
@@ -4419,67 +4415,67 @@
 )</f>
         <v>5200000</v>
       </c>
-      <c r="S8" s="43">
+      <c r="S8" s="29">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T8" s="43">
+      <c r="T8" s="29">
         <f t="shared" si="7"/>
         <v>2400000</v>
       </c>
-      <c r="U8" s="46">
+      <c r="U8" s="32">
         <f>IF(OR(G8="同年受取",S8=""),"",VLOOKUP(S8,税率表!$A$2:$C$8,2,TRUE))</f>
         <v>0.05</v>
       </c>
-      <c r="V8" s="43">
+      <c r="V8" s="29">
         <f>IF(U8="","",VLOOKUP(S8,税率表!$A$2:$C$8,3,TRUE))</f>
         <v>0</v>
       </c>
-      <c r="W8" s="43">
+      <c r="W8" s="29">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X8" s="46">
+      <c r="X8" s="32">
         <f>IF(OR(G8="同年受取",T8=""),"",VLOOKUP(T8,税率表!$A$2:$C$8,2,TRUE))</f>
         <v>0.1</v>
       </c>
-      <c r="Y8" s="43">
+      <c r="Y8" s="29">
         <f>IF(X8="","",VLOOKUP(T8,税率表!$A$2:$C$8,3,TRUE))</f>
         <v>97500</v>
       </c>
-      <c r="Z8" s="43">
+      <c r="Z8" s="29">
         <f t="shared" si="9"/>
         <v>145492</v>
       </c>
-      <c r="AA8" s="43">
+      <c r="AA8" s="29">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AB8" s="43">
+      <c r="AB8" s="29">
         <f t="shared" si="11"/>
         <v>240000</v>
       </c>
-      <c r="AC8" s="43">
+      <c r="AC8" s="29">
         <f t="shared" si="12"/>
         <v>385492</v>
       </c>
-      <c r="AD8" s="43">
+      <c r="AD8" s="29">
         <f t="shared" si="13"/>
         <v>10614508</v>
       </c>
-      <c r="AE8" s="47" t="str">
+      <c r="AE8" s="33" t="str">
         <f t="shared" si="14"/>
         <v>No.2732：確認期間→前の金額/控除→換算年数→重複年度→後の控除調整→課税退職所得→税額</v>
       </c>
-      <c r="AF8" s="47">
+      <c r="AF8" s="33">
         <f t="shared" si="15"/>
         <v>22</v>
       </c>
-      <c r="AG8" s="47">
+      <c r="AG8" s="33">
         <f>IF(OR(J8="",K8="",G8="同年受取"),"",IF(J8&lt;K8,AF8,IF(G8="DC → 会社退職金",入力!$B$21,入力!$B$19)))</f>
         <v>15</v>
       </c>
-      <c r="AH8" s="48" t="str">
+      <c r="AH8" s="34" t="str">
         <f>IF(G8&lt;&gt;"同年受取","",_xlfn.LET(
 _xlpm.A開始,入力!$B$6,
 _xlpm.A終了,入力!$B$7,
@@ -4499,45 +4495,45 @@
 ))</f>
         <v/>
       </c>
-      <c r="AI8" s="49" t="str">
+      <c r="AI8" s="35" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AJ8" s="49" t="str">
+      <c r="AJ8" s="35" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AK8" s="50" t="str">
+      <c r="AK8" s="36" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AL8" s="49" t="str">
+      <c r="AL8" s="35" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AM8" s="49" t="str">
+      <c r="AM8" s="35" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN8" s="49" t="str">
+      <c r="AN8" s="35" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AO8" s="49" t="str">
+      <c r="AO8" s="35" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AP8" s="49" t="str">
+      <c r="AP8" s="35" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="AQ8" s="49">
+      <c r="AQ8" s="35">
         <f t="shared" si="24"/>
         <v>10614508</v>
       </c>
     </row>
     <row r="9" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="39">
+      <c r="A9" s="25">
         <v>6</v>
       </c>
       <c r="B9" s="5">
@@ -4546,35 +4542,35 @@
       <c r="C9" s="5">
         <v>49490</v>
       </c>
-      <c r="D9" s="40">
+      <c r="D9" s="26">
         <f>入力!$B$8</f>
         <v>49459</v>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="27">
         <f>入力!$B$13</f>
         <v>10000000</v>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="27">
         <f>入力!$B$9</f>
         <v>1000000</v>
       </c>
-      <c r="G9" s="42" t="str">
+      <c r="G9" s="28" t="str">
         <f t="shared" si="0"/>
         <v>同年受取</v>
       </c>
-      <c r="H9" s="42" t="str">
+      <c r="H9" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I9" s="42" t="str">
+      <c r="I9" s="28" t="str">
         <f t="shared" si="2"/>
         <v>同年合算</v>
       </c>
-      <c r="J9" s="41" t="str">
+      <c r="J9" s="27" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K9" s="41" t="str">
+      <c r="K9" s="27" t="str">
         <f>IF(G9="同年受取","",
  IF(G9="DC → 会社退職金",
    _xlfn.LET(
@@ -4591,11 +4587,11 @@
  "")))</f>
         <v/>
       </c>
-      <c r="L9" s="43" t="str">
+      <c r="L9" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M9" s="44" t="str">
+      <c r="M9" s="30" t="str">
         <f>_xlfn.LET(
  _xlpm.前判定,L9,
  _xlpm.前退,J9,
@@ -4623,11 +4619,11 @@
 )</f>
         <v/>
       </c>
-      <c r="N9" s="45" t="str">
+      <c r="N9" s="31" t="str">
         <f>IF(G9="同年受取","",IF(I9&lt;&gt;"対象","",MAX(IF(G9="DC → 会社退職金",入力!$B$10,入力!$B$6),IF(G9="DC → 会社退職金",入力!$B$6,入力!$B$10))))</f>
         <v/>
       </c>
-      <c r="O9" s="45" t="str">
+      <c r="O9" s="31" t="str">
         <f>_xlfn.LET(
   _xlpm.受取順,G9,
   _xlpm.対象,I9,
@@ -4670,11 +4666,11 @@
 )</f>
         <v/>
       </c>
-      <c r="P9" s="44" t="str">
+      <c r="P9" s="30" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q9" s="43" t="str">
+      <c r="Q9" s="29" t="str">
         <f>IF(G9="同年受取","",
 _xlfn.LET(
 _xlpm.受取順,G9,
@@ -4697,7 +4693,7 @@
 ))</f>
         <v/>
       </c>
-      <c r="R9" s="43" t="str">
+      <c r="R9" s="29" t="str">
         <f>IF(G9="同年受取","",
  _xlfn.LET(
   _xlpm.受取順,G9,
@@ -4736,67 +4732,67 @@
 )</f>
         <v/>
       </c>
-      <c r="S9" s="43" t="str">
+      <c r="S9" s="29" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="T9" s="43" t="str">
+      <c r="T9" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="U9" s="46" t="str">
+      <c r="U9" s="32" t="str">
         <f>IF(OR(G9="同年受取",S9=""),"",VLOOKUP(S9,税率表!$A$2:$C$8,2,TRUE))</f>
         <v/>
       </c>
-      <c r="V9" s="43" t="str">
+      <c r="V9" s="29" t="str">
         <f>IF(U9="","",VLOOKUP(S9,税率表!$A$2:$C$8,3,TRUE))</f>
         <v/>
       </c>
-      <c r="W9" s="43" t="str">
+      <c r="W9" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="X9" s="46" t="str">
+      <c r="X9" s="32" t="str">
         <f>IF(OR(G9="同年受取",T9=""),"",VLOOKUP(T9,税率表!$A$2:$C$8,2,TRUE))</f>
         <v/>
       </c>
-      <c r="Y9" s="43" t="str">
+      <c r="Y9" s="29" t="str">
         <f>IF(X9="","",VLOOKUP(T9,税率表!$A$2:$C$8,3,TRUE))</f>
         <v/>
       </c>
-      <c r="Z9" s="43" t="str">
+      <c r="Z9" s="29" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AA9" s="43" t="str">
+      <c r="AA9" s="29" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AB9" s="43" t="str">
+      <c r="AB9" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC9" s="43" t="str">
+      <c r="AC9" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AD9" s="43" t="str">
+      <c r="AD9" s="29" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AE9" s="47" t="str">
+      <c r="AE9" s="33" t="str">
         <f t="shared" si="14"/>
         <v>No.2735：同年の退職手当等を合算し、2制度の勤続期間を統合して退職所得控除額を計算</v>
       </c>
-      <c r="AF9" s="47" t="str">
+      <c r="AF9" s="33" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AG9" s="47" t="str">
+      <c r="AG9" s="33" t="str">
         <f>IF(OR(J9="",K9="",G9="同年受取"),"",IF(J9&lt;K9,AF9,IF(G9="DC → 会社退職金",入力!$B$21,入力!$B$19)))</f>
         <v/>
       </c>
-      <c r="AH9" s="48">
+      <c r="AH9" s="34">
         <f>IF(G9&lt;&gt;"同年受取","",_xlfn.LET(
 _xlpm.A開始,入力!$B$6,
 _xlpm.A終了,入力!$B$7,
@@ -4816,45 +4812,45 @@
 ))</f>
         <v>47</v>
       </c>
-      <c r="AI9" s="49">
+      <c r="AI9" s="35">
         <f t="shared" si="16"/>
         <v>26900000</v>
       </c>
-      <c r="AJ9" s="49">
+      <c r="AJ9" s="35">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AK9" s="50">
+      <c r="AK9" s="36">
         <f t="shared" si="18"/>
         <v>0.05</v>
       </c>
-      <c r="AL9" s="49">
+      <c r="AL9" s="35">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AM9" s="49">
+      <c r="AM9" s="35">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AN9" s="49">
+      <c r="AN9" s="35">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="AO9" s="49">
+      <c r="AO9" s="35">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AP9" s="49">
+      <c r="AP9" s="35">
         <f t="shared" si="23"/>
         <v>11000000</v>
       </c>
-      <c r="AQ9" s="49">
+      <c r="AQ9" s="35">
         <f t="shared" si="24"/>
         <v>11000000</v>
       </c>
     </row>
     <row r="10" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="39">
+      <c r="A10" s="25">
         <v>7</v>
       </c>
       <c r="B10" s="5">
@@ -4863,35 +4859,35 @@
       <c r="C10" s="5">
         <v>49856</v>
       </c>
-      <c r="D10" s="40">
+      <c r="D10" s="26">
         <f>入力!$B$8</f>
         <v>49459</v>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="27">
         <f>入力!$B$13</f>
         <v>10000000</v>
       </c>
-      <c r="F10" s="41">
+      <c r="F10" s="27">
         <f>入力!$B$9</f>
         <v>1000000</v>
       </c>
-      <c r="G10" s="42" t="str">
+      <c r="G10" s="28" t="str">
         <f t="shared" si="0"/>
         <v>会社退職金 → DC</v>
       </c>
-      <c r="H10" s="42">
+      <c r="H10" s="28">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="I10" s="42" t="str">
+      <c r="I10" s="28" t="str">
         <f t="shared" si="2"/>
         <v>対象</v>
       </c>
-      <c r="J10" s="41">
+      <c r="J10" s="27">
         <f t="shared" si="3"/>
         <v>1000000</v>
       </c>
-      <c r="K10" s="41">
+      <c r="K10" s="27">
         <f>IF(G10="同年受取","",
  IF(G10="DC → 会社退職金",
    _xlfn.LET(
@@ -4908,11 +4904,11 @@
  "")))</f>
         <v>26900000</v>
       </c>
-      <c r="L10" s="43" t="str">
+      <c r="L10" s="29" t="str">
         <f t="shared" si="4"/>
         <v>該当</v>
       </c>
-      <c r="M10" s="44">
+      <c r="M10" s="30">
         <f>_xlfn.LET(
  _xlpm.前判定,L10,
  _xlpm.前退,J10,
@@ -4940,11 +4936,11 @@
 )</f>
         <v>2</v>
       </c>
-      <c r="N10" s="45">
+      <c r="N10" s="31">
         <f>IF(G10="同年受取","",IF(I10&lt;&gt;"対象","",MAX(IF(G10="DC → 会社退職金",入力!$B$10,入力!$B$6),IF(G10="DC → 会社退職金",入力!$B$6,入力!$B$10))))</f>
         <v>44652</v>
       </c>
-      <c r="O10" s="45">
+      <c r="O10" s="31">
         <f>_xlfn.LET(
   _xlpm.受取順,G10,
   _xlpm.対象,I10,
@@ -4987,11 +4983,11 @@
 )</f>
         <v>33328</v>
       </c>
-      <c r="P10" s="44">
+      <c r="P10" s="30">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q10" s="43">
+      <c r="Q10" s="29">
         <f>IF(G10="同年受取","",
 _xlfn.LET(
 _xlpm.受取順,G10,
@@ -5014,7 +5010,7 @@
 ))</f>
         <v>26900000</v>
       </c>
-      <c r="R10" s="43">
+      <c r="R10" s="29">
         <f>IF(G10="同年受取","",
  _xlfn.LET(
   _xlpm.受取順,G10,
@@ -5053,67 +5049,67 @@
 )</f>
         <v>6000000</v>
       </c>
-      <c r="S10" s="43">
+      <c r="S10" s="29">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T10" s="43">
+      <c r="T10" s="29">
         <f t="shared" si="7"/>
         <v>2000000</v>
       </c>
-      <c r="U10" s="46">
+      <c r="U10" s="32">
         <f>IF(OR(G10="同年受取",S10=""),"",VLOOKUP(S10,税率表!$A$2:$C$8,2,TRUE))</f>
         <v>0.05</v>
       </c>
-      <c r="V10" s="43">
+      <c r="V10" s="29">
         <f>IF(U10="","",VLOOKUP(S10,税率表!$A$2:$C$8,3,TRUE))</f>
         <v>0</v>
       </c>
-      <c r="W10" s="43">
+      <c r="W10" s="29">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X10" s="46">
+      <c r="X10" s="32">
         <f>IF(OR(G10="同年受取",T10=""),"",VLOOKUP(T10,税率表!$A$2:$C$8,2,TRUE))</f>
         <v>0.1</v>
       </c>
-      <c r="Y10" s="43">
+      <c r="Y10" s="29">
         <f>IF(X10="","",VLOOKUP(T10,税率表!$A$2:$C$8,3,TRUE))</f>
         <v>97500</v>
       </c>
-      <c r="Z10" s="43">
+      <c r="Z10" s="29">
         <f t="shared" si="9"/>
         <v>104652</v>
       </c>
-      <c r="AA10" s="43">
+      <c r="AA10" s="29">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AB10" s="43">
+      <c r="AB10" s="29">
         <f t="shared" si="11"/>
         <v>200000</v>
       </c>
-      <c r="AC10" s="43">
+      <c r="AC10" s="29">
         <f t="shared" si="12"/>
         <v>304652</v>
       </c>
-      <c r="AD10" s="43">
+      <c r="AD10" s="29">
         <f t="shared" si="13"/>
         <v>10695348</v>
       </c>
-      <c r="AE10" s="47" t="str">
+      <c r="AE10" s="33" t="str">
         <f t="shared" si="14"/>
         <v>No.2732：確認期間→前の金額/控除→換算年数→重複年度→後の控除調整→課税退職所得→税額</v>
       </c>
-      <c r="AF10" s="47">
+      <c r="AF10" s="33">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
-      <c r="AG10" s="47">
+      <c r="AG10" s="33">
         <f>IF(OR(J10="",K10="",G10="同年受取"),"",IF(J10&lt;K10,AF10,IF(G10="DC → 会社退職金",入力!$B$21,入力!$B$19)))</f>
         <v>2</v>
       </c>
-      <c r="AH10" s="48" t="str">
+      <c r="AH10" s="34" t="str">
         <f>IF(G10&lt;&gt;"同年受取","",_xlfn.LET(
 _xlpm.A開始,入力!$B$6,
 _xlpm.A終了,入力!$B$7,
@@ -5133,45 +5129,45 @@
 ))</f>
         <v/>
       </c>
-      <c r="AI10" s="49" t="str">
+      <c r="AI10" s="35" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AJ10" s="49" t="str">
+      <c r="AJ10" s="35" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AK10" s="50" t="str">
+      <c r="AK10" s="36" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AL10" s="49" t="str">
+      <c r="AL10" s="35" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AM10" s="49" t="str">
+      <c r="AM10" s="35" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN10" s="49" t="str">
+      <c r="AN10" s="35" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AO10" s="49" t="str">
+      <c r="AO10" s="35" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AP10" s="49" t="str">
+      <c r="AP10" s="35" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="AQ10" s="49">
+      <c r="AQ10" s="35">
         <f t="shared" si="24"/>
         <v>10695348</v>
       </c>
     </row>
     <row r="11" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="39">
+      <c r="A11" s="25">
         <v>8</v>
       </c>
       <c r="B11" s="5">
@@ -5180,35 +5176,35 @@
       <c r="C11" s="5">
         <v>50221</v>
       </c>
-      <c r="D11" s="40">
+      <c r="D11" s="26">
         <f>入力!$B$8</f>
         <v>49459</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="27">
         <f>入力!$B$13</f>
         <v>10000000</v>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="27">
         <f>入力!$B$9</f>
         <v>1000000</v>
       </c>
-      <c r="G11" s="42" t="str">
+      <c r="G11" s="28" t="str">
         <f t="shared" si="0"/>
         <v>会社退職金 → DC</v>
       </c>
-      <c r="H11" s="42">
+      <c r="H11" s="28">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="I11" s="42" t="str">
+      <c r="I11" s="28" t="str">
         <f t="shared" si="2"/>
         <v>対象</v>
       </c>
-      <c r="J11" s="41">
+      <c r="J11" s="27">
         <f t="shared" si="3"/>
         <v>1000000</v>
       </c>
-      <c r="K11" s="41">
+      <c r="K11" s="27">
         <f>IF(G11="同年受取","",
  IF(G11="DC → 会社退職金",
    _xlfn.LET(
@@ -5225,11 +5221,11 @@
  "")))</f>
         <v>26900000</v>
       </c>
-      <c r="L11" s="43" t="str">
+      <c r="L11" s="29" t="str">
         <f t="shared" si="4"/>
         <v>該当</v>
       </c>
-      <c r="M11" s="44">
+      <c r="M11" s="30">
         <f>_xlfn.LET(
  _xlpm.前判定,L11,
  _xlpm.前退,J11,
@@ -5257,11 +5253,11 @@
 )</f>
         <v>2</v>
       </c>
-      <c r="N11" s="45">
+      <c r="N11" s="31">
         <f>IF(G11="同年受取","",IF(I11&lt;&gt;"対象","",MAX(IF(G11="DC → 会社退職金",入力!$B$10,入力!$B$6),IF(G11="DC → 会社退職金",入力!$B$6,入力!$B$10))))</f>
         <v>44652</v>
       </c>
-      <c r="O11" s="45">
+      <c r="O11" s="31">
         <f>_xlfn.LET(
   _xlpm.受取順,G11,
   _xlpm.対象,I11,
@@ -5304,11 +5300,11 @@
 )</f>
         <v>33328</v>
       </c>
-      <c r="P11" s="44">
+      <c r="P11" s="30">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="43">
+      <c r="Q11" s="29">
         <f>IF(G11="同年受取","",
 _xlfn.LET(
 _xlpm.受取順,G11,
@@ -5331,7 +5327,7 @@
 ))</f>
         <v>26900000</v>
       </c>
-      <c r="R11" s="43">
+      <c r="R11" s="29">
         <f>IF(G11="同年受取","",
  _xlfn.LET(
   _xlpm.受取順,G11,
@@ -5370,67 +5366,67 @@
 )</f>
         <v>6400000</v>
       </c>
-      <c r="S11" s="43">
+      <c r="S11" s="29">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T11" s="43">
+      <c r="T11" s="29">
         <f t="shared" si="7"/>
         <v>1800000</v>
       </c>
-      <c r="U11" s="46">
+      <c r="U11" s="32">
         <f>IF(OR(G11="同年受取",S11=""),"",VLOOKUP(S11,税率表!$A$2:$C$8,2,TRUE))</f>
         <v>0.05</v>
       </c>
-      <c r="V11" s="43">
+      <c r="V11" s="29">
         <f>IF(U11="","",VLOOKUP(S11,税率表!$A$2:$C$8,3,TRUE))</f>
         <v>0</v>
       </c>
-      <c r="W11" s="43">
+      <c r="W11" s="29">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X11" s="46">
+      <c r="X11" s="32">
         <f>IF(OR(G11="同年受取",T11=""),"",VLOOKUP(T11,税率表!$A$2:$C$8,2,TRUE))</f>
         <v>0.05</v>
       </c>
-      <c r="Y11" s="43">
+      <c r="Y11" s="29">
         <f>IF(X11="","",VLOOKUP(T11,税率表!$A$2:$C$8,3,TRUE))</f>
         <v>0</v>
       </c>
-      <c r="Z11" s="43">
+      <c r="Z11" s="29">
         <f t="shared" si="9"/>
         <v>91890</v>
       </c>
-      <c r="AA11" s="43">
+      <c r="AA11" s="29">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AB11" s="43">
+      <c r="AB11" s="29">
         <f t="shared" si="11"/>
         <v>180000</v>
       </c>
-      <c r="AC11" s="43">
+      <c r="AC11" s="29">
         <f t="shared" si="12"/>
         <v>271890</v>
       </c>
-      <c r="AD11" s="43">
+      <c r="AD11" s="29">
         <f t="shared" si="13"/>
         <v>10728110</v>
       </c>
-      <c r="AE11" s="47" t="str">
+      <c r="AE11" s="33" t="str">
         <f t="shared" si="14"/>
         <v>No.2732：確認期間→前の金額/控除→換算年数→重複年度→後の控除調整→課税退職所得→税額</v>
       </c>
-      <c r="AF11" s="47">
+      <c r="AF11" s="33">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
-      <c r="AG11" s="47">
+      <c r="AG11" s="33">
         <f>IF(OR(J11="",K11="",G11="同年受取"),"",IF(J11&lt;K11,AF11,IF(G11="DC → 会社退職金",入力!$B$21,入力!$B$19)))</f>
         <v>2</v>
       </c>
-      <c r="AH11" s="48" t="str">
+      <c r="AH11" s="34" t="str">
         <f>IF(G11&lt;&gt;"同年受取","",_xlfn.LET(
 _xlpm.A開始,入力!$B$6,
 _xlpm.A終了,入力!$B$7,
@@ -5450,45 +5446,45 @@
 ))</f>
         <v/>
       </c>
-      <c r="AI11" s="49" t="str">
+      <c r="AI11" s="35" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AJ11" s="49" t="str">
+      <c r="AJ11" s="35" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AK11" s="50" t="str">
+      <c r="AK11" s="36" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AL11" s="49" t="str">
+      <c r="AL11" s="35" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AM11" s="49" t="str">
+      <c r="AM11" s="35" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN11" s="49" t="str">
+      <c r="AN11" s="35" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AO11" s="49" t="str">
+      <c r="AO11" s="35" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AP11" s="49" t="str">
+      <c r="AP11" s="35" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="AQ11" s="49">
+      <c r="AQ11" s="35">
         <f t="shared" si="24"/>
         <v>10728110</v>
       </c>
     </row>
     <row r="12" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="39">
+      <c r="A12" s="25">
         <v>9</v>
       </c>
       <c r="B12" s="5">
@@ -5497,35 +5493,35 @@
       <c r="C12" s="5">
         <v>50586</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="26">
         <f>入力!$B$8</f>
         <v>49459</v>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="27">
         <f>入力!$B$13</f>
         <v>10000000</v>
       </c>
-      <c r="F12" s="41">
+      <c r="F12" s="27">
         <f>入力!$B$9</f>
         <v>1000000</v>
       </c>
-      <c r="G12" s="42" t="str">
+      <c r="G12" s="28" t="str">
         <f t="shared" si="0"/>
         <v>会社退職金 → DC</v>
       </c>
-      <c r="H12" s="42">
+      <c r="H12" s="28">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="I12" s="42" t="str">
+      <c r="I12" s="28" t="str">
         <f t="shared" si="2"/>
         <v>対象</v>
       </c>
-      <c r="J12" s="41">
+      <c r="J12" s="27">
         <f t="shared" si="3"/>
         <v>1000000</v>
       </c>
-      <c r="K12" s="41">
+      <c r="K12" s="27">
         <f>IF(G12="同年受取","",
  IF(G12="DC → 会社退職金",
    _xlfn.LET(
@@ -5542,11 +5538,11 @@
  "")))</f>
         <v>26900000</v>
       </c>
-      <c r="L12" s="43" t="str">
+      <c r="L12" s="29" t="str">
         <f t="shared" si="4"/>
         <v>該当</v>
       </c>
-      <c r="M12" s="44">
+      <c r="M12" s="30">
         <f>_xlfn.LET(
  _xlpm.前判定,L12,
  _xlpm.前退,J12,
@@ -5574,11 +5570,11 @@
 )</f>
         <v>2</v>
       </c>
-      <c r="N12" s="45">
+      <c r="N12" s="31">
         <f>IF(G12="同年受取","",IF(I12&lt;&gt;"対象","",MAX(IF(G12="DC → 会社退職金",入力!$B$10,入力!$B$6),IF(G12="DC → 会社退職金",入力!$B$6,入力!$B$10))))</f>
         <v>44652</v>
       </c>
-      <c r="O12" s="45">
+      <c r="O12" s="31">
         <f>_xlfn.LET(
   _xlpm.受取順,G12,
   _xlpm.対象,I12,
@@ -5621,11 +5617,11 @@
 )</f>
         <v>33328</v>
       </c>
-      <c r="P12" s="44">
+      <c r="P12" s="30">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="43">
+      <c r="Q12" s="29">
         <f>IF(G12="同年受取","",
 _xlfn.LET(
 _xlpm.受取順,G12,
@@ -5648,7 +5644,7 @@
 ))</f>
         <v>26900000</v>
       </c>
-      <c r="R12" s="43">
+      <c r="R12" s="29">
         <f>IF(G12="同年受取","",
  _xlfn.LET(
   _xlpm.受取順,G12,
@@ -5687,67 +5683,67 @@
 )</f>
         <v>6800000</v>
       </c>
-      <c r="S12" s="43">
+      <c r="S12" s="29">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T12" s="43">
+      <c r="T12" s="29">
         <f t="shared" si="7"/>
         <v>1600000</v>
       </c>
-      <c r="U12" s="46">
+      <c r="U12" s="32">
         <f>IF(OR(G12="同年受取",S12=""),"",VLOOKUP(S12,税率表!$A$2:$C$8,2,TRUE))</f>
         <v>0.05</v>
       </c>
-      <c r="V12" s="43">
+      <c r="V12" s="29">
         <f>IF(U12="","",VLOOKUP(S12,税率表!$A$2:$C$8,3,TRUE))</f>
         <v>0</v>
       </c>
-      <c r="W12" s="43">
+      <c r="W12" s="29">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X12" s="46">
+      <c r="X12" s="32">
         <f>IF(OR(G12="同年受取",T12=""),"",VLOOKUP(T12,税率表!$A$2:$C$8,2,TRUE))</f>
         <v>0.05</v>
       </c>
-      <c r="Y12" s="43">
+      <c r="Y12" s="29">
         <f>IF(X12="","",VLOOKUP(T12,税率表!$A$2:$C$8,3,TRUE))</f>
         <v>0</v>
       </c>
-      <c r="Z12" s="43">
+      <c r="Z12" s="29">
         <f t="shared" si="9"/>
         <v>81680</v>
       </c>
-      <c r="AA12" s="43">
+      <c r="AA12" s="29">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AB12" s="43">
+      <c r="AB12" s="29">
         <f t="shared" si="11"/>
         <v>160000</v>
       </c>
-      <c r="AC12" s="43">
+      <c r="AC12" s="29">
         <f t="shared" si="12"/>
         <v>241680</v>
       </c>
-      <c r="AD12" s="43">
+      <c r="AD12" s="29">
         <f t="shared" si="13"/>
         <v>10758320</v>
       </c>
-      <c r="AE12" s="47" t="str">
+      <c r="AE12" s="33" t="str">
         <f t="shared" si="14"/>
         <v>No.2732：確認期間→前の金額/控除→換算年数→重複年度→後の控除調整→課税退職所得→税額</v>
       </c>
-      <c r="AF12" s="47">
+      <c r="AF12" s="33">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
-      <c r="AG12" s="47">
+      <c r="AG12" s="33">
         <f>IF(OR(J12="",K12="",G12="同年受取"),"",IF(J12&lt;K12,AF12,IF(G12="DC → 会社退職金",入力!$B$21,入力!$B$19)))</f>
         <v>2</v>
       </c>
-      <c r="AH12" s="48" t="str">
+      <c r="AH12" s="34" t="str">
         <f>IF(G12&lt;&gt;"同年受取","",_xlfn.LET(
 _xlpm.A開始,入力!$B$6,
 _xlpm.A終了,入力!$B$7,
@@ -5767,45 +5763,45 @@
 ))</f>
         <v/>
       </c>
-      <c r="AI12" s="49" t="str">
+      <c r="AI12" s="35" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AJ12" s="49" t="str">
+      <c r="AJ12" s="35" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AK12" s="50" t="str">
+      <c r="AK12" s="36" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AL12" s="49" t="str">
+      <c r="AL12" s="35" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AM12" s="49" t="str">
+      <c r="AM12" s="35" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN12" s="49" t="str">
+      <c r="AN12" s="35" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AO12" s="49" t="str">
+      <c r="AO12" s="35" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AP12" s="49" t="str">
+      <c r="AP12" s="35" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="AQ12" s="49">
+      <c r="AQ12" s="35">
         <f t="shared" si="24"/>
         <v>10758320</v>
       </c>
     </row>
     <row r="13" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="39">
+      <c r="A13" s="25">
         <v>10</v>
       </c>
       <c r="B13" s="5">
@@ -5814,35 +5810,35 @@
       <c r="C13" s="5">
         <v>50951</v>
       </c>
-      <c r="D13" s="40">
+      <c r="D13" s="26">
         <f>入力!$B$8</f>
         <v>49459</v>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="27">
         <f>入力!$B$13</f>
         <v>10000000</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="27">
         <f>入力!$B$9</f>
         <v>1000000</v>
       </c>
-      <c r="G13" s="42" t="str">
+      <c r="G13" s="28" t="str">
         <f t="shared" si="0"/>
         <v>会社退職金 → DC</v>
       </c>
-      <c r="H13" s="42">
+      <c r="H13" s="28">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="I13" s="42" t="str">
+      <c r="I13" s="28" t="str">
         <f t="shared" si="2"/>
         <v>対象</v>
       </c>
-      <c r="J13" s="41">
+      <c r="J13" s="27">
         <f t="shared" si="3"/>
         <v>1000000</v>
       </c>
-      <c r="K13" s="41">
+      <c r="K13" s="27">
         <f>IF(G13="同年受取","",
  IF(G13="DC → 会社退職金",
    _xlfn.LET(
@@ -5859,11 +5855,11 @@
  "")))</f>
         <v>26900000</v>
       </c>
-      <c r="L13" s="43" t="str">
+      <c r="L13" s="29" t="str">
         <f t="shared" si="4"/>
         <v>該当</v>
       </c>
-      <c r="M13" s="44">
+      <c r="M13" s="30">
         <f>_xlfn.LET(
  _xlpm.前判定,L13,
  _xlpm.前退,J13,
@@ -5891,11 +5887,11 @@
 )</f>
         <v>2</v>
       </c>
-      <c r="N13" s="45">
+      <c r="N13" s="31">
         <f>IF(G13="同年受取","",IF(I13&lt;&gt;"対象","",MAX(IF(G13="DC → 会社退職金",入力!$B$10,入力!$B$6),IF(G13="DC → 会社退職金",入力!$B$6,入力!$B$10))))</f>
         <v>44652</v>
       </c>
-      <c r="O13" s="45">
+      <c r="O13" s="31">
         <f>_xlfn.LET(
   _xlpm.受取順,G13,
   _xlpm.対象,I13,
@@ -5938,11 +5934,11 @@
 )</f>
         <v>33328</v>
       </c>
-      <c r="P13" s="44">
+      <c r="P13" s="30">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q13" s="43">
+      <c r="Q13" s="29">
         <f>IF(G13="同年受取","",
 _xlfn.LET(
 _xlpm.受取順,G13,
@@ -5965,7 +5961,7 @@
 ))</f>
         <v>26900000</v>
       </c>
-      <c r="R13" s="43">
+      <c r="R13" s="29">
         <f>IF(G13="同年受取","",
  _xlfn.LET(
   _xlpm.受取順,G13,
@@ -6004,67 +6000,67 @@
 )</f>
         <v>7200000</v>
       </c>
-      <c r="S13" s="43">
+      <c r="S13" s="29">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T13" s="43">
+      <c r="T13" s="29">
         <f t="shared" si="7"/>
         <v>1400000</v>
       </c>
-      <c r="U13" s="46">
+      <c r="U13" s="32">
         <f>IF(OR(G13="同年受取",S13=""),"",VLOOKUP(S13,税率表!$A$2:$C$8,2,TRUE))</f>
         <v>0.05</v>
       </c>
-      <c r="V13" s="43">
+      <c r="V13" s="29">
         <f>IF(U13="","",VLOOKUP(S13,税率表!$A$2:$C$8,3,TRUE))</f>
         <v>0</v>
       </c>
-      <c r="W13" s="43">
+      <c r="W13" s="29">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X13" s="46">
+      <c r="X13" s="32">
         <f>IF(OR(G13="同年受取",T13=""),"",VLOOKUP(T13,税率表!$A$2:$C$8,2,TRUE))</f>
         <v>0.05</v>
       </c>
-      <c r="Y13" s="43">
+      <c r="Y13" s="29">
         <f>IF(X13="","",VLOOKUP(T13,税率表!$A$2:$C$8,3,TRUE))</f>
         <v>0</v>
       </c>
-      <c r="Z13" s="43">
+      <c r="Z13" s="29">
         <f t="shared" si="9"/>
         <v>71470</v>
       </c>
-      <c r="AA13" s="43">
+      <c r="AA13" s="29">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AB13" s="43">
+      <c r="AB13" s="29">
         <f t="shared" si="11"/>
         <v>140000</v>
       </c>
-      <c r="AC13" s="43">
+      <c r="AC13" s="29">
         <f t="shared" si="12"/>
         <v>211470</v>
       </c>
-      <c r="AD13" s="43">
+      <c r="AD13" s="29">
         <f t="shared" si="13"/>
         <v>10788530</v>
       </c>
-      <c r="AE13" s="47" t="str">
+      <c r="AE13" s="33" t="str">
         <f t="shared" si="14"/>
         <v>No.2732：確認期間→前の金額/控除→換算年数→重複年度→後の控除調整→課税退職所得→税額</v>
       </c>
-      <c r="AF13" s="47">
+      <c r="AF13" s="33">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
-      <c r="AG13" s="47">
+      <c r="AG13" s="33">
         <f>IF(OR(J13="",K13="",G13="同年受取"),"",IF(J13&lt;K13,AF13,IF(G13="DC → 会社退職金",入力!$B$21,入力!$B$19)))</f>
         <v>2</v>
       </c>
-      <c r="AH13" s="48" t="str">
+      <c r="AH13" s="34" t="str">
         <f>IF(G13&lt;&gt;"同年受取","",_xlfn.LET(
 _xlpm.A開始,入力!$B$6,
 _xlpm.A終了,入力!$B$7,
@@ -6084,139 +6080,139 @@
 ))</f>
         <v/>
       </c>
-      <c r="AI13" s="49" t="str">
+      <c r="AI13" s="35" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AJ13" s="49" t="str">
+      <c r="AJ13" s="35" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AK13" s="50" t="str">
+      <c r="AK13" s="36" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AL13" s="49" t="str">
+      <c r="AL13" s="35" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AM13" s="49" t="str">
+      <c r="AM13" s="35" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN13" s="49" t="str">
+      <c r="AN13" s="35" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AO13" s="49" t="str">
+      <c r="AO13" s="35" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AP13" s="49" t="str">
+      <c r="AP13" s="35" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="AQ13" s="49">
+      <c r="AQ13" s="35">
         <f t="shared" si="24"/>
         <v>10788530</v>
       </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.4">
-      <c r="AJ14" s="17"/>
+      <c r="AJ14" s="11"/>
     </row>
     <row r="15" spans="1:43" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="51" t="s">
+      <c r="A15" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="O15" s="52"/>
+      <c r="O15" s="38"/>
     </row>
     <row r="16" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="53" t="s">
+      <c r="A16" s="39" t="s">
         <v>137</v>
       </c>
-      <c r="B16" s="53"/>
-      <c r="C16" s="53"/>
-      <c r="D16" s="53"/>
-      <c r="E16" s="54" t="s">
+      <c r="B16" s="39"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="F16" s="55"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="55"/>
-      <c r="I16" s="55"/>
-      <c r="J16" s="55"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B17" s="55"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="55"/>
-      <c r="H17" s="55"/>
-      <c r="I17" s="55"/>
-      <c r="J17" s="55"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B18" s="55"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="55"/>
-      <c r="H18" s="55"/>
-      <c r="I18" s="55"/>
-      <c r="J18" s="55"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A19" s="56" t="s">
+      <c r="A19" s="42" t="s">
         <v>139</v>
       </c>
-      <c r="C19" s="54" t="s">
+      <c r="C19" s="40" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A20" s="56" t="s">
+      <c r="A20" s="42" t="s">
         <v>215</v>
       </c>
-      <c r="C20" s="54" t="s">
+      <c r="C20" s="40" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A21" s="56"/>
-      <c r="C21" s="54" t="s">
+      <c r="A21" s="42"/>
+      <c r="C21" s="40" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A22" s="56"/>
-      <c r="C22" s="54" t="s">
+      <c r="A22" s="42"/>
+      <c r="C22" s="40" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A23" s="56" t="s">
+      <c r="A23" s="42" t="s">
         <v>141</v>
       </c>
-      <c r="C23" s="54" t="s">
+      <c r="C23" s="40" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A24" s="56" t="s">
+      <c r="A24" s="42" t="s">
         <v>143</v>
       </c>
-      <c r="C24" s="54" t="s">
+      <c r="C24" s="40" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A25" s="56" t="s">
+      <c r="A25" s="42" t="s">
         <v>145</v>
       </c>
-      <c r="B25" s="57" t="s">
+      <c r="B25" s="43" t="s">
         <v>146</v>
       </c>
     </row>
@@ -6245,36 +6241,36 @@
   <dimension ref="A1:Y41"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="18" style="16" customWidth="1"/>
-    <col min="2" max="2" width="12.875" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="17"/>
-    <col min="4" max="4" width="15.125" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="13" width="9" style="17"/>
-    <col min="14" max="14" width="15.125" style="16" customWidth="1"/>
-    <col min="15" max="15" width="34.375" style="16" customWidth="1"/>
-    <col min="16" max="16" width="9" style="17"/>
-    <col min="17" max="17" width="14.875" style="16" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="34.125" style="16" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6" style="16" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.5" style="16" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9" style="17"/>
-    <col min="22" max="22" width="73.875" style="16" customWidth="1"/>
-    <col min="23" max="16384" width="9" style="17"/>
+    <col min="1" max="1" width="18" style="10" customWidth="1"/>
+    <col min="2" max="2" width="12.875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="11"/>
+    <col min="4" max="4" width="15.125" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="13" width="9" style="11"/>
+    <col min="14" max="14" width="15.125" style="10" customWidth="1"/>
+    <col min="15" max="15" width="34.375" style="10" customWidth="1"/>
+    <col min="16" max="16" width="9" style="11"/>
+    <col min="17" max="17" width="14.875" style="10" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="34.125" style="10" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6" style="10" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9" style="11"/>
+    <col min="22" max="22" width="73.875" style="10" customWidth="1"/>
+    <col min="23" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="10" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="11" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A4" s="58" t="s">
+      <c r="A4" s="44" t="s">
         <v>148</v>
       </c>
       <c r="B4" s="1">
@@ -6282,7 +6278,7 @@
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A5" s="58" t="s">
+      <c r="A5" s="44" t="s">
         <v>149</v>
       </c>
       <c r="B5" s="1">
@@ -6290,43 +6286,43 @@
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A6" s="58" t="s">
+      <c r="A6" s="44" t="s">
         <v>150</v>
       </c>
       <c r="B6" s="1">
         <v>49460</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="E6" s="17" t="str">
+      <c r="E6" s="11" t="str">
         <f>DATEDIF(B4, B6, "Y") &amp; "歳" &amp; DATEDIF(B4, B6, "YM") &amp; "ヶ月"</f>
         <v>65歳0ヶ月</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A7" s="58" t="s">
+      <c r="A7" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="B7" s="59">
+      <c r="B7" s="45">
         <f>IF(DATEDIF(B5,B6+1,"M")=0, 1, CEILING(DATEDIF(B5,B6+1,"M")/12, 1))</f>
         <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A8" s="58" t="s">
+      <c r="A8" s="44" t="s">
         <v>141</v>
       </c>
-      <c r="B8" s="60">
+      <c r="B8" s="46">
         <f>IF(B7&lt;=20, MAX(400000*B7, 800000), 8000000+700000*(B7-20))</f>
         <v>26900000</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="11" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A9" s="58" t="s">
+      <c r="A9" s="44" t="s">
         <v>154</v>
       </c>
       <c r="B9" s="4">
@@ -6334,346 +6330,346 @@
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A10" s="58" t="s">
+      <c r="A10" s="44" t="s">
         <v>143</v>
       </c>
-      <c r="B10" s="60">
+      <c r="B10" s="46">
         <f>MAX(0, FLOOR((B9-B8)/2, 1000))</f>
         <v>0</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="11" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A11" s="58" t="s">
+      <c r="A11" s="44" t="s">
         <v>156</v>
       </c>
-      <c r="B11" s="61">
+      <c r="B11" s="47">
         <f>VLOOKUP(B10,tabletax,3,TRUE)</f>
         <v>0.05</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="R11" s="62"/>
-      <c r="S11" s="62"/>
-      <c r="T11" s="62"/>
+      <c r="R11" s="48"/>
+      <c r="S11" s="48"/>
+      <c r="T11" s="48"/>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A12" s="58" t="s">
+      <c r="A12" s="44" t="s">
         <v>158</v>
       </c>
-      <c r="B12" s="60">
+      <c r="B12" s="46">
         <f>VLOOKUP(B10,tabletax,4,TRUE)</f>
         <v>0</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="N12" s="62" t="s">
+      <c r="N12" s="48" t="s">
         <v>160</v>
       </c>
-      <c r="O12" s="62"/>
-      <c r="P12" s="62"/>
-      <c r="Q12" s="62"/>
-      <c r="R12" s="62" t="s">
+      <c r="O12" s="48"/>
+      <c r="P12" s="48"/>
+      <c r="Q12" s="48"/>
+      <c r="R12" s="48" t="s">
         <v>159</v>
       </c>
-      <c r="S12" s="62"/>
-      <c r="T12" s="62"/>
-      <c r="V12" s="62" t="s">
+      <c r="S12" s="48"/>
+      <c r="T12" s="48"/>
+      <c r="V12" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="W12" s="62"/>
-      <c r="X12" s="62"/>
-      <c r="Y12" s="62"/>
+      <c r="W12" s="48"/>
+      <c r="X12" s="48"/>
+      <c r="Y12" s="48"/>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A13" s="58" t="s">
+      <c r="A13" s="44" t="s">
         <v>162</v>
       </c>
-      <c r="B13" s="60">
+      <c r="B13" s="46">
         <f>FLOOR((B10*B11-B12)*1.021, 1)</f>
         <v>0</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="N13" s="62" t="s">
+      <c r="N13" s="48" t="s">
         <v>167</v>
       </c>
-      <c r="O13" s="62"/>
-      <c r="P13" s="62"/>
-      <c r="Q13" s="63" t="s">
+      <c r="O13" s="48"/>
+      <c r="P13" s="48"/>
+      <c r="Q13" s="49" t="s">
         <v>163</v>
       </c>
-      <c r="R13" s="63" t="s">
+      <c r="R13" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="S13" s="63" t="s">
+      <c r="S13" s="49" t="s">
         <v>165</v>
       </c>
-      <c r="T13" s="63" t="s">
+      <c r="T13" s="49" t="s">
         <v>166</v>
       </c>
-      <c r="V13" s="62" t="s">
+      <c r="V13" s="48" t="s">
         <v>168</v>
       </c>
-      <c r="W13" s="62"/>
-      <c r="X13" s="62"/>
-      <c r="Y13" s="62"/>
+      <c r="W13" s="48"/>
+      <c r="X13" s="48"/>
+      <c r="Y13" s="48"/>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A14" s="58" t="s">
+      <c r="A14" s="44" t="s">
         <v>169</v>
       </c>
-      <c r="B14" s="60">
+      <c r="B14" s="46">
         <f>FLOOR(B10 * 0.1, 100)</f>
         <v>0</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="N14" s="62" t="s">
+      <c r="N14" s="48" t="s">
         <v>172</v>
       </c>
-      <c r="O14" s="62"/>
-      <c r="P14" s="62"/>
-      <c r="Q14" s="63">
+      <c r="O14" s="48"/>
+      <c r="P14" s="48"/>
+      <c r="Q14" s="49">
         <v>0</v>
       </c>
-      <c r="R14" s="63" t="s">
+      <c r="R14" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="S14" s="64">
+      <c r="S14" s="50">
         <v>0.05</v>
       </c>
-      <c r="T14" s="63">
+      <c r="T14" s="49">
         <v>0</v>
       </c>
-      <c r="V14" s="62" t="s">
+      <c r="V14" s="48" t="s">
         <v>173</v>
       </c>
-      <c r="W14" s="62"/>
-      <c r="X14" s="62"/>
-      <c r="Y14" s="62"/>
+      <c r="W14" s="48"/>
+      <c r="X14" s="48"/>
+      <c r="Y14" s="48"/>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A15" s="58" t="s">
+      <c r="A15" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="B15" s="65">
+      <c r="B15" s="51">
         <f>B13+B14</f>
         <v>0</v>
       </c>
-      <c r="N15" s="63" t="s">
+      <c r="N15" s="49" t="s">
         <v>176</v>
       </c>
-      <c r="O15" s="63" t="s">
+      <c r="O15" s="49" t="s">
         <v>141</v>
       </c>
-      <c r="P15" s="62"/>
-      <c r="Q15" s="66">
+      <c r="P15" s="48"/>
+      <c r="Q15" s="52">
         <v>1950000</v>
       </c>
-      <c r="R15" s="66" t="s">
+      <c r="R15" s="52" t="s">
         <v>175</v>
       </c>
-      <c r="S15" s="64">
+      <c r="S15" s="50">
         <v>0.1</v>
       </c>
-      <c r="T15" s="66">
+      <c r="T15" s="52">
         <v>97500</v>
       </c>
-      <c r="V15" s="62" t="s">
+      <c r="V15" s="48" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A16" s="58" t="s">
+      <c r="A16" s="44" t="s">
         <v>174</v>
       </c>
-      <c r="B16" s="60">
+      <c r="B16" s="46">
         <f>B9-B15</f>
         <v>10000000</v>
       </c>
-      <c r="N16" s="67" t="s">
+      <c r="N16" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="O16" s="67" t="s">
+      <c r="O16" s="53" t="s">
         <v>180</v>
       </c>
-      <c r="P16" s="62"/>
-      <c r="Q16" s="66">
+      <c r="P16" s="48"/>
+      <c r="Q16" s="52">
         <v>3300000</v>
       </c>
-      <c r="R16" s="66" t="s">
+      <c r="R16" s="52" t="s">
         <v>178</v>
       </c>
-      <c r="S16" s="64">
+      <c r="S16" s="50">
         <v>0.2</v>
       </c>
-      <c r="T16" s="66">
+      <c r="T16" s="52">
         <v>427500</v>
       </c>
-      <c r="V16" s="62"/>
-      <c r="W16" s="62"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="62"/>
+      <c r="V16" s="48"/>
+      <c r="W16" s="48"/>
+      <c r="X16" s="48"/>
+      <c r="Y16" s="48"/>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="B17" s="49"/>
-      <c r="N17" s="68"/>
-      <c r="O17" s="69" t="s">
+      <c r="B17" s="35"/>
+      <c r="N17" s="54"/>
+      <c r="O17" s="55" t="s">
         <v>182</v>
       </c>
-      <c r="P17" s="62"/>
-      <c r="Q17" s="66">
+      <c r="P17" s="48"/>
+      <c r="Q17" s="52">
         <v>6950000</v>
       </c>
-      <c r="R17" s="66" t="s">
+      <c r="R17" s="52" t="s">
         <v>181</v>
       </c>
-      <c r="S17" s="64">
+      <c r="S17" s="50">
         <v>0.23</v>
       </c>
-      <c r="T17" s="66">
+      <c r="T17" s="52">
         <v>636000</v>
       </c>
-      <c r="V17" s="62"/>
-      <c r="W17" s="62"/>
-      <c r="X17" s="62"/>
-      <c r="Y17" s="62"/>
+      <c r="V17" s="48"/>
+      <c r="W17" s="48"/>
+      <c r="X17" s="48"/>
+      <c r="Y17" s="48"/>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="N18" s="63" t="s">
+      <c r="N18" s="49" t="s">
         <v>184</v>
       </c>
-      <c r="O18" s="63" t="s">
+      <c r="O18" s="49" t="s">
         <v>185</v>
       </c>
-      <c r="P18" s="62"/>
-      <c r="Q18" s="66">
+      <c r="P18" s="48"/>
+      <c r="Q18" s="52">
         <v>9000000</v>
       </c>
-      <c r="R18" s="66" t="s">
+      <c r="R18" s="52" t="s">
         <v>183</v>
       </c>
-      <c r="S18" s="64">
+      <c r="S18" s="50">
         <v>0.33</v>
       </c>
-      <c r="T18" s="66">
+      <c r="T18" s="52">
         <v>1536000</v>
       </c>
-      <c r="V18" s="62"/>
-      <c r="W18" s="62"/>
-      <c r="X18" s="62"/>
-      <c r="Y18" s="62"/>
+      <c r="V18" s="48"/>
+      <c r="W18" s="48"/>
+      <c r="X18" s="48"/>
+      <c r="Y18" s="48"/>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="N19" s="62"/>
-      <c r="O19" s="62"/>
-      <c r="P19" s="62"/>
-      <c r="Q19" s="66">
+      <c r="N19" s="48"/>
+      <c r="O19" s="48"/>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="52">
         <v>18000000</v>
       </c>
-      <c r="R19" s="66" t="s">
+      <c r="R19" s="52" t="s">
         <v>186</v>
       </c>
-      <c r="S19" s="64">
+      <c r="S19" s="50">
         <v>0.4</v>
       </c>
-      <c r="T19" s="66">
+      <c r="T19" s="52">
         <v>2796000</v>
       </c>
-      <c r="V19" s="62"/>
-      <c r="W19" s="62"/>
-      <c r="X19" s="62"/>
-      <c r="Y19" s="62"/>
+      <c r="V19" s="48"/>
+      <c r="W19" s="48"/>
+      <c r="X19" s="48"/>
+      <c r="Y19" s="48"/>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="N20" s="62"/>
-      <c r="O20" s="62"/>
-      <c r="P20" s="62"/>
-      <c r="Q20" s="66">
+      <c r="N20" s="48"/>
+      <c r="O20" s="48"/>
+      <c r="P20" s="48"/>
+      <c r="Q20" s="52">
         <v>40000000</v>
       </c>
-      <c r="R20" s="66" t="s">
+      <c r="R20" s="52" t="s">
         <v>187</v>
       </c>
-      <c r="S20" s="64">
+      <c r="S20" s="50">
         <v>0.45</v>
       </c>
-      <c r="T20" s="66">
+      <c r="T20" s="52">
         <v>4796000</v>
       </c>
-      <c r="V20" s="62"/>
-      <c r="W20" s="62"/>
-      <c r="X20" s="62"/>
-      <c r="Y20" s="62"/>
+      <c r="V20" s="48"/>
+      <c r="W20" s="48"/>
+      <c r="X20" s="48"/>
+      <c r="Y20" s="48"/>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="N21" s="62"/>
-      <c r="O21" s="62"/>
-      <c r="P21" s="62"/>
-      <c r="V21" s="62"/>
-      <c r="W21" s="62"/>
-      <c r="X21" s="62"/>
-      <c r="Y21" s="62"/>
+      <c r="N21" s="48"/>
+      <c r="O21" s="48"/>
+      <c r="P21" s="48"/>
+      <c r="V21" s="48"/>
+      <c r="W21" s="48"/>
+      <c r="X21" s="48"/>
+      <c r="Y21" s="48"/>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="W22" s="62"/>
-      <c r="X22" s="62"/>
-      <c r="Y22" s="62"/>
+      <c r="W22" s="48"/>
+      <c r="X22" s="48"/>
+      <c r="Y22" s="48"/>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="W23" s="62"/>
-      <c r="X23" s="62"/>
-      <c r="Y23" s="62"/>
+      <c r="W23" s="48"/>
+      <c r="X23" s="48"/>
+      <c r="Y23" s="48"/>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="11" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="11" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A35" s="70" t="s">
+      <c r="A35" s="56" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="11" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A37" s="70" t="s">
+      <c r="A37" s="56" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="11" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A39" s="70" t="s">
+      <c r="A39" s="56" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A40" s="17" t="s">
+      <c r="A40" s="11" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A41" s="70" t="s">
+      <c r="A41" s="56" t="s">
         <v>196</v>
       </c>
     </row>
@@ -6710,136 +6706,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" x14ac:dyDescent="0.5">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="71" t="s">
         <v>197</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="73" t="s">
         <v>199</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="73" t="s">
         <v>201</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="72"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
+      <c r="B7" s="72"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="72"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
+      <c r="B8" s="72"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="72"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="73" t="s">
         <v>203</v>
       </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
+      <c r="C9" s="72"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
+      <c r="B10" s="72"/>
+      <c r="C10" s="72"/>
+      <c r="D10" s="72"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="72"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
+      <c r="B11" s="72"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="72"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="72"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="72"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
+      <c r="B16" s="72"/>
+      <c r="C16" s="72"/>
+      <c r="D16" s="72"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>206</v>
       </c>
-      <c r="B17" s="71" t="s">
+      <c r="B17" s="74" t="s">
         <v>190</v>
       </c>
-      <c r="C17" s="71"/>
-      <c r="D17" s="71"/>
+      <c r="C17" s="74"/>
+      <c r="D17" s="74"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>207</v>
       </c>
-      <c r="B18" s="71" t="s">
+      <c r="B18" s="74" t="s">
         <v>208</v>
       </c>
-      <c r="C18" s="71"/>
-      <c r="D18" s="71"/>
+      <c r="C18" s="74"/>
+      <c r="D18" s="74"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19" s="2" t="s">
@@ -6889,96 +6885,95 @@
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="13" style="13" customWidth="1"/>
-    <col min="2" max="3" width="12" style="13" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="14"/>
+    <col min="1" max="1" width="13" style="2" customWidth="1"/>
+    <col min="2" max="3" width="12" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="57" t="s">
         <v>209</v>
       </c>
-      <c r="B1" s="73" t="s">
+      <c r="B1" s="58" t="s">
         <v>165</v>
       </c>
-      <c r="C1" s="72" t="s">
+      <c r="C1" s="57" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2" s="74">
+      <c r="A2" s="59">
         <v>0</v>
       </c>
-      <c r="B2" s="75">
+      <c r="B2" s="60">
         <v>0.05</v>
       </c>
-      <c r="C2" s="74">
+      <c r="C2" s="59">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" s="74">
+      <c r="A3" s="59">
         <v>1950000</v>
       </c>
-      <c r="B3" s="75">
+      <c r="B3" s="60">
         <v>0.1</v>
       </c>
-      <c r="C3" s="74">
+      <c r="C3" s="59">
         <v>97500</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" s="74">
+      <c r="A4" s="59">
         <v>3300000</v>
       </c>
-      <c r="B4" s="75">
+      <c r="B4" s="60">
         <v>0.2</v>
       </c>
-      <c r="C4" s="74">
+      <c r="C4" s="59">
         <v>427500</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" s="74">
+      <c r="A5" s="59">
         <v>6950000</v>
       </c>
-      <c r="B5" s="75">
+      <c r="B5" s="60">
         <v>0.23</v>
       </c>
-      <c r="C5" s="74">
+      <c r="C5" s="59">
         <v>636000</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" s="74">
+      <c r="A6" s="59">
         <v>9000000</v>
       </c>
-      <c r="B6" s="75">
+      <c r="B6" s="60">
         <v>0.33</v>
       </c>
-      <c r="C6" s="74">
+      <c r="C6" s="59">
         <v>1536000</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" s="74">
+      <c r="A7" s="59">
         <v>18000000</v>
       </c>
-      <c r="B7" s="75">
+      <c r="B7" s="60">
         <v>0.4</v>
       </c>
-      <c r="C7" s="74">
+      <c r="C7" s="59">
         <v>2796000</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" s="74">
+      <c r="A8" s="59">
         <v>40000000</v>
       </c>
-      <c r="B8" s="75">
+      <c r="B8" s="60">
         <v>0.45</v>
       </c>
-      <c r="C8" s="74">
+      <c r="C8" s="59">
         <v>4796000</v>
       </c>
     </row>

--- a/退職金_確定拠出年金_重複調整シミュレーション.xlsx
+++ b/退職金_確定拠出年金_重複調整シミュレーション.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\personal\克彦\40_個人年金\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2775A7F1-AD0F-4FFD-B397-E20A4ADFED41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFDB2ADF-5613-446A-8450-993EF540E693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1485,7 +1485,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$R$12:$T$20" spid="_x0000_s4333"/>
+                  <a14:cameraTool cellRange="$R$12:$T$20" spid="_x0000_s4348"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1550,7 +1550,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$N$12:$O$18" spid="_x0000_s4334"/>
+                  <a14:cameraTool cellRange="$N$12:$O$18" spid="_x0000_s4349"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1615,7 +1615,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$V$12:$V$15" spid="_x0000_s4335"/>
+                  <a14:cameraTool cellRange="$V$12:$V$15" spid="_x0000_s4350"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -6217,7 +6217,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="1kOhctHesE3Svbe7M/35wdUHyKUEb/Q1Hrrf6nrqrNR4piwo7pB2QtbBdSvMdPgyLl/fGA6j5IsBlrajiITJRQ==" saltValue="P1QniNEId9DfGsZ3MJr3NA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="gNcGem/x1ieUJlYEi63BB3ds73ga+ZfZR0xtpr9U4Rig++pmAmgRwZiWdSE5reFxkur/cBxllcNFS3sq4FC2SQ==" saltValue="OFcRpzxzxnCzx162J9qdAA==" spinCount="100000" sheet="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
